--- a/GITT_data_analysis/GITT_corrected_current_based_pulse_detection.xlsx
+++ b/GITT_data_analysis/GITT_corrected_current_based_pulse_detection.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,56 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Pulse Start Time (s)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Pulse End Time (s)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Relaxation Start Time (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Relaxation End Time (s)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Pulse Start Voltage (V)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Pulse End Voltage (V)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Relaxation Start Voltage (V)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Relaxation End Voltage (V)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Capacity_ends (mAh/g)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Capacity_starts (mAh/g)</t>
         </is>
@@ -482,3330 +470,3106 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7.999999797902976</v>
+        <v>4205.048095206035</v>
       </c>
       <c r="B2" t="n">
-        <v>595.0001849690303</v>
+        <v>609.9999845901011</v>
       </c>
       <c r="C2" t="n">
-        <v>610.0481845888849</v>
+        <v>625.0481842099535</v>
       </c>
       <c r="D2" t="n">
-        <v>4190.048095387644</v>
+        <v>8375.048444719045</v>
       </c>
       <c r="E2" t="n">
-        <v>2.42663407325744</v>
+        <v>2.23271059989929</v>
       </c>
       <c r="F2" t="n">
-        <v>2.39670753479003</v>
+        <v>2.19645953178405</v>
       </c>
       <c r="G2" t="n">
-        <v>2.39909672737121</v>
+        <v>2.22139048576355</v>
       </c>
       <c r="H2" t="n">
-        <v>2.40348291397094</v>
+        <v>2.22192502021789</v>
       </c>
       <c r="I2" t="n">
-        <v>13.6045938682195</v>
+        <v>13.9840932393779</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13.9840932393779</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4210.000095146112</v>
+        <v>8395.048444476888</v>
       </c>
       <c r="B3" t="n">
-        <v>4805.0004879423</v>
+        <v>4800.000488002848</v>
       </c>
       <c r="C3" t="n">
-        <v>4820.04848776014</v>
+        <v>4815.048487820652</v>
       </c>
       <c r="D3" t="n">
-        <v>8380.048444658496</v>
+        <v>12585.04879374774</v>
       </c>
       <c r="E3" t="n">
-        <v>2.40350198745727</v>
+        <v>2.22211599349975</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3892638683319</v>
+        <v>2.18952989578247</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3925085067749</v>
+        <v>2.21249485015869</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39621114730835</v>
+        <v>2.21881341934204</v>
       </c>
       <c r="I3" t="n">
-        <v>27.7905667406479</v>
+        <v>27.7347143737287</v>
       </c>
       <c r="J3" t="n">
-        <v>13.9534249304071</v>
+        <v>27.9677610143441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8400.048444416339</v>
+        <v>12605.04879350558</v>
       </c>
       <c r="B4" t="n">
-        <v>8995.000837213152</v>
+        <v>9010.000637031564</v>
       </c>
       <c r="C4" t="n">
-        <v>9010.048837030956</v>
+        <v>9025.048836849348</v>
       </c>
       <c r="D4" t="n">
-        <v>12590.04879368719</v>
+        <v>16775.04914301863</v>
       </c>
       <c r="E4" t="n">
-        <v>2.39617300033569</v>
+        <v>2.21883249282836</v>
       </c>
       <c r="F4" t="n">
-        <v>2.38548493385314</v>
+        <v>2.18563556671142</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38819432258606</v>
+        <v>2.21188378334045</v>
       </c>
       <c r="H4" t="n">
-        <v>2.39149689674377</v>
+        <v>2.21688532829284</v>
       </c>
       <c r="I4" t="n">
-        <v>41.5115166554937</v>
+        <v>41.9517193399875</v>
       </c>
       <c r="J4" t="n">
-        <v>27.9068403494598</v>
+        <v>41.9517193399875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12610.00079344566</v>
+        <v>16795.04914277647</v>
       </c>
       <c r="B5" t="n">
-        <v>13205.00118624185</v>
+        <v>13200.0011863024</v>
       </c>
       <c r="C5" t="n">
-        <v>13220.04918605965</v>
+        <v>13215.0491861202</v>
       </c>
       <c r="D5" t="n">
-        <v>16780.04914295808</v>
+        <v>20985.04949204732</v>
       </c>
       <c r="E5" t="n">
-        <v>2.39136338233947</v>
+        <v>2.21675181388855</v>
       </c>
       <c r="F5" t="n">
-        <v>2.382488489151</v>
+        <v>2.18137860298156</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38558030128479</v>
+        <v>2.20617604255676</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38855767250061</v>
+        <v>2.21474742889404</v>
       </c>
       <c r="I5" t="n">
-        <v>55.6974672376893</v>
+        <v>55.7028494913118</v>
       </c>
       <c r="J5" t="n">
-        <v>41.8603498546079</v>
+        <v>55.9359370455308</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16800.04914271596</v>
+        <v>21005.04949180517</v>
       </c>
       <c r="B6" t="n">
-        <v>17395.00153551274</v>
+        <v>17410.00133533112</v>
       </c>
       <c r="C6" t="n">
-        <v>17410.04953533054</v>
+        <v>17425.04953514893</v>
       </c>
       <c r="D6" t="n">
-        <v>20990.04949198677</v>
+        <v>25175.04984131814</v>
       </c>
       <c r="E6" t="n">
-        <v>2.38859605789184</v>
+        <v>2.21486186981201</v>
       </c>
       <c r="F6" t="n">
-        <v>2.38000726699829</v>
+        <v>2.17599534988403</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38234233856201</v>
+        <v>2.20560336112976</v>
       </c>
       <c r="H6" t="n">
-        <v>2.38592386245727</v>
+        <v>2.21194124221801</v>
       </c>
       <c r="I6" t="n">
-        <v>69.418299092448</v>
+        <v>69.9208998396582</v>
       </c>
       <c r="J6" t="n">
-        <v>55.8137408622881</v>
+        <v>69.9208998396582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21010.00149174521</v>
+        <v>25195.04984107602</v>
       </c>
       <c r="B7" t="n">
-        <v>21605.00188454143</v>
+        <v>21600.00188460198</v>
       </c>
       <c r="C7" t="n">
-        <v>21620.04988435924</v>
+        <v>21615.04988441975</v>
       </c>
       <c r="D7" t="n">
-        <v>25180.04984125763</v>
+        <v>29385.05019034687</v>
       </c>
       <c r="E7" t="n">
-        <v>2.38588571548461</v>
+        <v>2.21205568313598</v>
       </c>
       <c r="F7" t="n">
-        <v>2.37798428535461</v>
+        <v>2.17000126838684</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38092350959777</v>
+        <v>2.20020103454589</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38370990753173</v>
+        <v>2.20903944969177</v>
       </c>
       <c r="I7" t="n">
-        <v>83.6043764541665</v>
+        <v>83.6722887026865</v>
       </c>
       <c r="J7" t="n">
-        <v>69.76713100950479</v>
+        <v>83.90537080046271</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25200.04984101547</v>
+        <v>29405.05019010475</v>
       </c>
       <c r="B8" t="n">
-        <v>25795.00223381232</v>
+        <v>25810.0020336307</v>
       </c>
       <c r="C8" t="n">
-        <v>25810.05023363009</v>
+        <v>25825.05023344848</v>
       </c>
       <c r="D8" t="n">
-        <v>29390.05019028636</v>
+        <v>33575.0505508922</v>
       </c>
       <c r="E8" t="n">
-        <v>2.38384366035461</v>
+        <v>2.20909667015075</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3759229183197</v>
+        <v>2.16211724281311</v>
       </c>
       <c r="G8" t="n">
-        <v>2.37809371948242</v>
+        <v>2.20054459571838</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38195395469665</v>
+        <v>2.20651960372924</v>
       </c>
       <c r="I8" t="n">
-        <v>97.32517769139049</v>
+        <v>97.890292359478</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7206512321081</v>
+        <v>97.890292359478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29410.00219004479</v>
+        <v>33595.05055092948</v>
       </c>
       <c r="B9" t="n">
-        <v>30005.00258284102</v>
+        <v>30000.00258290153</v>
       </c>
       <c r="C9" t="n">
-        <v>30020.05058265882</v>
+        <v>30015.05058271937</v>
       </c>
       <c r="D9" t="n">
-        <v>33580.05055090153</v>
+        <v>37785.05095873392</v>
       </c>
       <c r="E9" t="n">
-        <v>2.38166785240173</v>
+        <v>2.20665335655212</v>
       </c>
       <c r="F9" t="n">
-        <v>2.37353730201721</v>
+        <v>2.1522479057312</v>
       </c>
       <c r="G9" t="n">
-        <v>2.37674355506897</v>
+        <v>2.1947796344757</v>
       </c>
       <c r="H9" t="n">
-        <v>2.37983560562133</v>
+        <v>2.20497345924377</v>
       </c>
       <c r="I9" t="n">
-        <v>111.511087140188</v>
+        <v>111.641315520396</v>
       </c>
       <c r="J9" t="n">
-        <v>97.6740060510961</v>
+        <v>111.874394003324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33600.05055093877</v>
+        <v>37805.05095877116</v>
       </c>
       <c r="B10" t="n">
-        <v>34195.0029520469</v>
+        <v>34210.00275207484</v>
       </c>
       <c r="C10" t="n">
-        <v>34210.05095207498</v>
+        <v>34225.05095210293</v>
       </c>
       <c r="D10" t="n">
-        <v>37790.05095874296</v>
+        <v>41975.05136653836</v>
       </c>
       <c r="E10" t="n">
-        <v>2.37977838516235</v>
+        <v>2.20508790016174</v>
       </c>
       <c r="F10" t="n">
-        <v>2.37027359008789</v>
+        <v>2.13896131515502</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37320351600647</v>
+        <v>2.19411134719848</v>
       </c>
       <c r="H10" t="n">
-        <v>2.37714433670043</v>
+        <v>2.20382809638977</v>
       </c>
       <c r="I10" t="n">
-        <v>125.23186963094</v>
+        <v>125.858343013121</v>
       </c>
       <c r="J10" t="n">
-        <v>111.627360803607</v>
+        <v>125.858343013121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>37810.00295878032</v>
+        <v>41995.0513665756</v>
       </c>
       <c r="B11" t="n">
-        <v>38405.0033598888</v>
+        <v>38400.0033598794</v>
       </c>
       <c r="C11" t="n">
-        <v>38420.05135991652</v>
+        <v>38415.05135990712</v>
       </c>
       <c r="D11" t="n">
-        <v>41980.05136654776</v>
+        <v>46185.05177438004</v>
       </c>
       <c r="E11" t="n">
-        <v>2.37704896926879</v>
+        <v>2.20375180244445</v>
       </c>
       <c r="F11" t="n">
-        <v>2.36584568023681</v>
+        <v>2.12573218345642</v>
       </c>
       <c r="G11" t="n">
-        <v>2.36941456794738</v>
+        <v>2.18428015708923</v>
       </c>
       <c r="H11" t="n">
-        <v>2.37361359596252</v>
+        <v>2.20251083374023</v>
       </c>
       <c r="I11" t="n">
-        <v>139.418035546311</v>
+        <v>139.609573658741</v>
       </c>
       <c r="J11" t="n">
-        <v>125.580698851551</v>
+        <v>139.842646951733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>42000.051366585</v>
+        <v>46205.05177441728</v>
       </c>
       <c r="B12" t="n">
-        <v>42595.00376769324</v>
+        <v>42610.00356772092</v>
       </c>
       <c r="C12" t="n">
-        <v>42610.05176772096</v>
+        <v>42625.0517677488</v>
       </c>
       <c r="D12" t="n">
-        <v>46190.05177438945</v>
+        <v>50375.05218218448</v>
       </c>
       <c r="E12" t="n">
-        <v>2.37370896339416</v>
+        <v>2.20251083374023</v>
       </c>
       <c r="F12" t="n">
-        <v>2.35926103591918</v>
+        <v>2.11311411857605</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36206078529357</v>
+        <v>2.18315386772155</v>
       </c>
       <c r="H12" t="n">
-        <v>2.36588382720947</v>
+        <v>2.20062088966369</v>
       </c>
       <c r="I12" t="n">
-        <v>153.138864905701</v>
+        <v>153.826619299995</v>
       </c>
       <c r="J12" t="n">
-        <v>139.534311977663</v>
+        <v>153.826619299995</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>46210.00377442644</v>
+        <v>50395.05218222172</v>
       </c>
       <c r="B13" t="n">
-        <v>46805.00417553492</v>
+        <v>46800.00417552552</v>
       </c>
       <c r="C13" t="n">
-        <v>46820.05217556264</v>
+        <v>46815.0521755536</v>
       </c>
       <c r="D13" t="n">
-        <v>50380.05218219387</v>
+        <v>54585.05259002616</v>
       </c>
       <c r="E13" t="n">
-        <v>2.36575007438659</v>
+        <v>2.20048737525939</v>
       </c>
       <c r="F13" t="n">
-        <v>2.34412574768066</v>
+        <v>2.10059118270874</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3476185798645</v>
+        <v>2.171471118927</v>
       </c>
       <c r="H13" t="n">
-        <v>2.35303902626037</v>
+        <v>2.19640207290649</v>
       </c>
       <c r="I13" t="n">
-        <v>167.324793029094</v>
+        <v>167.577108647908</v>
       </c>
       <c r="J13" t="n">
-        <v>153.487695668082</v>
+        <v>167.810181471988</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50400.05218223112</v>
+        <v>54605.05259006339</v>
       </c>
       <c r="B14" t="n">
-        <v>50995.00458333936</v>
+        <v>51010.00438336741</v>
       </c>
       <c r="C14" t="n">
-        <v>51010.05258336744</v>
+        <v>51025.05258339528</v>
       </c>
       <c r="D14" t="n">
-        <v>54590.05259003556</v>
+        <v>58775.0529978306</v>
       </c>
       <c r="E14" t="n">
-        <v>2.35301995277404</v>
+        <v>2.19640207290649</v>
       </c>
       <c r="F14" t="n">
-        <v>2.31952404975891</v>
+        <v>2.08644580841064</v>
       </c>
       <c r="G14" t="n">
-        <v>2.32117652893066</v>
+        <v>2.17030668258667</v>
       </c>
       <c r="H14" t="n">
-        <v>2.33305597305297</v>
+        <v>2.18956804275512</v>
       </c>
       <c r="I14" t="n">
-        <v>181.045589340769</v>
+        <v>181.794560075164</v>
       </c>
       <c r="J14" t="n">
-        <v>167.441066099215</v>
+        <v>181.794560075164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54610.00459007292</v>
+        <v>58795.05299786785</v>
       </c>
       <c r="B15" t="n">
-        <v>55205.00499118104</v>
+        <v>55200.00499117164</v>
       </c>
       <c r="C15" t="n">
-        <v>55220.05299120912</v>
+        <v>55215.05299119971</v>
       </c>
       <c r="D15" t="n">
-        <v>58780.05299784</v>
+        <v>62985.05340567264</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3330750465393</v>
+        <v>2.18972086906433</v>
       </c>
       <c r="F15" t="n">
-        <v>2.27934837341308</v>
+        <v>2.07084941864013</v>
       </c>
       <c r="G15" t="n">
-        <v>2.28343272209167</v>
+        <v>2.15640926361084</v>
       </c>
       <c r="H15" t="n">
-        <v>2.30186963081359</v>
+        <v>2.18164587020874</v>
       </c>
       <c r="I15" t="n">
-        <v>195.231481250966</v>
+        <v>195.545603528904</v>
       </c>
       <c r="J15" t="n">
-        <v>181.394417294182</v>
+        <v>195.778653843291</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>58800.05299787724</v>
+        <v>63005.05340570988</v>
       </c>
       <c r="B16" t="n">
-        <v>59395.00539898549</v>
+        <v>59410.00519901352</v>
       </c>
       <c r="C16" t="n">
-        <v>59410.05339901357</v>
+        <v>59425.0533990414</v>
       </c>
       <c r="D16" t="n">
-        <v>62990.05340568168</v>
+        <v>67175.05342271976</v>
       </c>
       <c r="E16" t="n">
-        <v>2.30196523666381</v>
+        <v>2.18174123764038</v>
       </c>
       <c r="F16" t="n">
-        <v>2.23581337928772</v>
+        <v>2.04918265342712</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2375648021698</v>
+        <v>2.15364146232605</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26163673400878</v>
+        <v>2.17200565338134</v>
       </c>
       <c r="I16" t="n">
-        <v>208.952198577518</v>
+        <v>209.762010655731</v>
       </c>
       <c r="J16" t="n">
-        <v>195.347755286194</v>
+        <v>209.762010655731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>63010.00540571904</v>
+        <v>67195.05341796504</v>
       </c>
       <c r="B17" t="n">
-        <v>63605.00580682715</v>
+        <v>63600.00580681812</v>
       </c>
       <c r="C17" t="n">
-        <v>63620.05380685523</v>
+        <v>63615.05380684584</v>
       </c>
       <c r="D17" t="n">
-        <v>67180.05342154116</v>
+        <v>71385.05282684833</v>
       </c>
       <c r="E17" t="n">
-        <v>2.26156044006347</v>
+        <v>2.17210102081298</v>
       </c>
       <c r="F17" t="n">
-        <v>2.19779443740844</v>
+        <v>2.01541304588317</v>
       </c>
       <c r="G17" t="n">
-        <v>2.20180249214172</v>
+        <v>2.13021826744079</v>
       </c>
       <c r="H17" t="n">
-        <v>2.22336959838867</v>
+        <v>2.16847395896911</v>
       </c>
       <c r="I17" t="n">
-        <v>223.138078702671</v>
+        <v>223.512996873202</v>
       </c>
       <c r="J17" t="n">
-        <v>209.301026322342</v>
+        <v>223.746065559921</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>67200.05341677276</v>
+        <v>71405.05282215445</v>
       </c>
       <c r="B18" t="n">
-        <v>67795.00567605</v>
+        <v>67810.00547252988</v>
       </c>
       <c r="C18" t="n">
-        <v>67810.05367251804</v>
+        <v>67825.05366895199</v>
       </c>
       <c r="D18" t="n">
-        <v>71390.05282567476</v>
+        <v>75575.05223576796</v>
       </c>
       <c r="E18" t="n">
-        <v>2.22317862510681</v>
+        <v>2.16851210594177</v>
       </c>
       <c r="F18" t="n">
-        <v>2.16729521751403</v>
+        <v>2.01485967636108</v>
       </c>
       <c r="G18" t="n">
-        <v>2.16878342628479</v>
+        <v>2.13812136650085</v>
       </c>
       <c r="H18" t="n">
-        <v>2.19157242774963</v>
+        <v>2.16639328002929</v>
       </c>
       <c r="I18" t="n">
-        <v>236.858780052116</v>
+        <v>237.729940060053</v>
       </c>
       <c r="J18" t="n">
-        <v>223.254352028924</v>
+        <v>237.729940060053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>71410.00482097956</v>
+        <v>75595.05223102188</v>
       </c>
       <c r="B19" t="n">
-        <v>72005.00508021169</v>
+        <v>72000.00508140359</v>
       </c>
       <c r="C19" t="n">
-        <v>72020.0530766466</v>
+        <v>72015.05307782015</v>
       </c>
       <c r="D19" t="n">
-        <v>75580.0522345944</v>
+        <v>79785.0516398958</v>
       </c>
       <c r="E19" t="n">
-        <v>2.19147706031799</v>
+        <v>2.16616415977478</v>
       </c>
       <c r="F19" t="n">
-        <v>2.13813185691833</v>
+        <v>2.00325298309326</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14198732376098</v>
+        <v>2.1107850074768</v>
       </c>
       <c r="H19" t="n">
-        <v>2.16458487510681</v>
+        <v>2.16578245162963</v>
       </c>
       <c r="I19" t="n">
-        <v>251.04459917623</v>
+        <v>251.480528770089</v>
       </c>
       <c r="J19" t="n">
-        <v>237.207609282291</v>
+        <v>251.713593401885</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>75600.0522298296</v>
+        <v>79805.05163520192</v>
       </c>
       <c r="B20" t="n">
-        <v>76195.00448909856</v>
+        <v>76210.00428557808</v>
       </c>
       <c r="C20" t="n">
-        <v>76210.0524855666</v>
+        <v>76225.05248200885</v>
       </c>
       <c r="D20" t="n">
-        <v>79790.05163872223</v>
+        <v>83975.0510488158</v>
       </c>
       <c r="E20" t="n">
-        <v>2.16475677490234</v>
+        <v>2.16585874557495</v>
       </c>
       <c r="F20" t="n">
-        <v>2.11019015312194</v>
+        <v>1.99912965297699</v>
       </c>
       <c r="G20" t="n">
-        <v>2.11202692985534</v>
+        <v>2.13025641441345</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1405177116394</v>
+        <v>2.16933298110961</v>
       </c>
       <c r="I20" t="n">
-        <v>264.765343649783</v>
+        <v>265.697594451553</v>
       </c>
       <c r="J20" t="n">
-        <v>251.160871940365</v>
+        <v>265.697594451553</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79810.00363403604</v>
+        <v>83995.05104407801</v>
       </c>
       <c r="B21" t="n">
-        <v>80405.0038932678</v>
+        <v>80400.00389446008</v>
       </c>
       <c r="C21" t="n">
-        <v>80420.05188969444</v>
+        <v>80415.05189087195</v>
       </c>
       <c r="D21" t="n">
-        <v>83980.05104764224</v>
+        <v>88185.05045294472</v>
       </c>
       <c r="E21" t="n">
-        <v>2.14034581184387</v>
+        <v>2.16927576065063</v>
       </c>
       <c r="F21" t="n">
-        <v>2.07761073112487</v>
+        <v>2.00653648376464</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08184766769409</v>
+        <v>2.10437083244323</v>
       </c>
       <c r="H21" t="n">
-        <v>2.11753821372985</v>
+        <v>2.17471623420715</v>
       </c>
       <c r="I21" t="n">
-        <v>278.951196502724</v>
+        <v>279.448309323615</v>
       </c>
       <c r="J21" t="n">
-        <v>265.114172847578</v>
+        <v>279.681375557928</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84000.05104288609</v>
+        <v>88205.05044825084</v>
       </c>
       <c r="B22" t="n">
-        <v>84595.0033021464</v>
+        <v>84610.00309862629</v>
       </c>
       <c r="C22" t="n">
-        <v>84610.0512986148</v>
+        <v>84625.05129506605</v>
       </c>
       <c r="D22" t="n">
-        <v>88190.05045177117</v>
+        <v>92375.04986186471</v>
       </c>
       <c r="E22" t="n">
-        <v>2.11769104003906</v>
+        <v>2.17492628097534</v>
       </c>
       <c r="F22" t="n">
-        <v>2.06308627128601</v>
+        <v>2.0284514427185</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06745529174804</v>
+        <v>2.13277626037597</v>
       </c>
       <c r="H22" t="n">
-        <v>2.12585973739624</v>
+        <v>2.18069148063659</v>
       </c>
       <c r="I22" t="n">
-        <v>292.671971305983</v>
+        <v>293.66442381927</v>
       </c>
       <c r="J22" t="n">
-        <v>279.067468876514</v>
+        <v>293.66442381927</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88210.00244709036</v>
+        <v>92395.04985713592</v>
       </c>
       <c r="B23" t="n">
-        <v>88805.00270632464</v>
+        <v>88800.00270751692</v>
       </c>
       <c r="C23" t="n">
-        <v>88820.05070274336</v>
+        <v>88815.05070392952</v>
       </c>
       <c r="D23" t="n">
-        <v>92380.04986069116</v>
+        <v>96585.04926599977</v>
       </c>
       <c r="E23" t="n">
-        <v>2.12572622299194</v>
+        <v>2.1807677745819</v>
       </c>
       <c r="F23" t="n">
-        <v>2.08369898796081</v>
+        <v>2.04727387428283</v>
       </c>
       <c r="G23" t="n">
-        <v>2.089768409729</v>
+        <v>2.12493062019348</v>
       </c>
       <c r="H23" t="n">
-        <v>2.13708233833313</v>
+        <v>2.18617010116577</v>
       </c>
       <c r="I23" t="n">
-        <v>306.858063721258</v>
+        <v>307.41481652188</v>
       </c>
       <c r="J23" t="n">
-        <v>293.020800351128</v>
+        <v>307.647862013692</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>92400.049855944</v>
+        <v>96605.04926129976</v>
       </c>
       <c r="B24" t="n">
-        <v>92995.0021151946</v>
+        <v>93010.00191167413</v>
       </c>
       <c r="C24" t="n">
-        <v>93010.05011166335</v>
+        <v>93025.05010812324</v>
       </c>
       <c r="D24" t="n">
-        <v>96590.04926482007</v>
+        <v>100775.0486749136</v>
       </c>
       <c r="E24" t="n">
-        <v>2.13725399971008</v>
+        <v>2.1861891746521</v>
       </c>
       <c r="F24" t="n">
-        <v>2.09041714668273</v>
+        <v>2.06302285194397</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0930278301239</v>
+        <v>2.1409466266632</v>
       </c>
       <c r="H24" t="n">
-        <v>2.14089941978454</v>
+        <v>2.19044613838195</v>
       </c>
       <c r="I24" t="n">
-        <v>320.578873874782</v>
+        <v>321.630470762491</v>
       </c>
       <c r="J24" t="n">
-        <v>306.974339181389</v>
+        <v>321.630470762491</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96610.0012601382</v>
+        <v>100795.0486701931</v>
       </c>
       <c r="B25" t="n">
-        <v>97205.00151938111</v>
+        <v>97200.00152057339</v>
       </c>
       <c r="C25" t="n">
-        <v>97220.04951579444</v>
+        <v>97215.04951698672</v>
       </c>
       <c r="D25" t="n">
-        <v>100780.0486737401</v>
+        <v>104985.0480790555</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1409375667572</v>
+        <v>2.19050335884094</v>
       </c>
       <c r="F25" t="n">
-        <v>2.09333729743957</v>
+        <v>2.07314038276672</v>
       </c>
       <c r="G25" t="n">
-        <v>2.09896779060363</v>
+        <v>2.13646054267883</v>
       </c>
       <c r="H25" t="n">
-        <v>2.14296078681945</v>
+        <v>2.19359588623046</v>
       </c>
       <c r="I25" t="n">
-        <v>334.764779276041</v>
+        <v>335.380959070831</v>
       </c>
       <c r="J25" t="n">
-        <v>320.927701072633</v>
+        <v>335.614009984423</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100800.0486690012</v>
+        <v>105005.0480743472</v>
       </c>
       <c r="B26" t="n">
-        <v>101395.0009282439</v>
+        <v>101410.0007247216</v>
       </c>
       <c r="C26" t="n">
-        <v>101410.0489247116</v>
+        <v>101425.0489211804</v>
       </c>
       <c r="D26" t="n">
-        <v>104990.0480778679</v>
+        <v>109175.0474879611</v>
       </c>
       <c r="E26" t="n">
-        <v>2.14309430122375</v>
+        <v>2.19367241859436</v>
       </c>
       <c r="F26" t="n">
-        <v>2.09560871124267</v>
+        <v>2.07909631729126</v>
       </c>
       <c r="G26" t="n">
-        <v>2.09791779518127</v>
+        <v>2.1468071937561</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1446783542633</v>
+        <v>2.19584846496582</v>
       </c>
       <c r="I26" t="n">
-        <v>348.485805829742</v>
+        <v>349.598122306576</v>
       </c>
       <c r="J26" t="n">
-        <v>334.881052717449</v>
+        <v>349.598122306576</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105010.000073185</v>
+        <v>109195.0474832496</v>
       </c>
       <c r="B27" t="n">
-        <v>105605.0003324369</v>
+        <v>105600.0003336292</v>
       </c>
       <c r="C27" t="n">
-        <v>105620.0483288509</v>
+        <v>105615.0483300428</v>
       </c>
       <c r="D27" t="n">
-        <v>109180.0474867876</v>
+        <v>113385.0468921138</v>
       </c>
       <c r="E27" t="n">
-        <v>2.14475464820861</v>
+        <v>2.19602036476135</v>
       </c>
       <c r="F27" t="n">
-        <v>2.09530329704284</v>
+        <v>2.08329606056213</v>
       </c>
       <c r="G27" t="n">
-        <v>2.10112452507019</v>
+        <v>2.14151930809021</v>
       </c>
       <c r="H27" t="n">
-        <v>2.14544177055358</v>
+        <v>2.19768118858337</v>
       </c>
       <c r="I27" t="n">
-        <v>362.671724073766</v>
+        <v>363.350400083903</v>
       </c>
       <c r="J27" t="n">
-        <v>348.83463925729</v>
+        <v>363.583504789747</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109200.0474820573</v>
+        <v>113405.0468873965</v>
       </c>
       <c r="B28" t="n">
-        <v>109794.9997413004</v>
+        <v>109809.9995377698</v>
       </c>
       <c r="C28" t="n">
-        <v>109810.0477377598</v>
+        <v>109825.0477342376</v>
       </c>
       <c r="D28" t="n">
-        <v>113390.0468909215</v>
+        <v>117575.0463010104</v>
       </c>
       <c r="E28" t="n">
-        <v>2.14557552337646</v>
+        <v>2.19779562950134</v>
       </c>
       <c r="F28" t="n">
-        <v>2.09545588493347</v>
+        <v>2.08732390403747</v>
       </c>
       <c r="G28" t="n">
-        <v>2.09767723083496</v>
+        <v>2.1501669883728</v>
       </c>
       <c r="H28" t="n">
-        <v>2.14614796638488</v>
+        <v>2.19909381866455</v>
       </c>
       <c r="I28" t="n">
-        <v>376.392540322449</v>
+        <v>377.568437662215</v>
       </c>
       <c r="J28" t="n">
-        <v>362.787997531594</v>
+        <v>377.568437662215</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113409.9988862339</v>
+        <v>117595.0462963075</v>
       </c>
       <c r="B29" t="n">
-        <v>114004.9991454944</v>
+        <v>113999.9991466867</v>
       </c>
       <c r="C29" t="n">
-        <v>114020.0471419085</v>
+        <v>114015.0471431004</v>
       </c>
       <c r="D29" t="n">
-        <v>117580.0462998368</v>
+        <v>121785.0457051717</v>
       </c>
       <c r="E29" t="n">
-        <v>2.14610981941223</v>
+        <v>2.19909381866455</v>
       </c>
       <c r="F29" t="n">
-        <v>2.09526515007019</v>
+        <v>2.09240174293518</v>
       </c>
       <c r="G29" t="n">
-        <v>2.10129618644714</v>
+        <v>2.14505100250244</v>
       </c>
       <c r="H29" t="n">
-        <v>2.14664435386657</v>
+        <v>2.20025825500488</v>
       </c>
       <c r="I29" t="n">
-        <v>390.5784391961</v>
+        <v>391.319482819484</v>
       </c>
       <c r="J29" t="n">
-        <v>376.741368656104</v>
+        <v>391.552533455318</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117600.0462951156</v>
+        <v>121805.0457004458</v>
       </c>
       <c r="B30" t="n">
-        <v>118194.9985543583</v>
+        <v>118209.9983508184</v>
       </c>
       <c r="C30" t="n">
-        <v>118210.0465508087</v>
+        <v>118225.0465472884</v>
       </c>
       <c r="D30" t="n">
-        <v>121790.0457039798</v>
+        <v>125975.0451140604</v>
       </c>
       <c r="E30" t="n">
-        <v>2.14675879478454</v>
+        <v>2.20022010803222</v>
       </c>
       <c r="F30" t="n">
-        <v>2.09566593170166</v>
+        <v>2.09597158432006</v>
       </c>
       <c r="G30" t="n">
-        <v>2.09759712219238</v>
+        <v>2.1528205871582</v>
       </c>
       <c r="H30" t="n">
-        <v>2.14752221107482</v>
+        <v>2.20109820365905</v>
       </c>
       <c r="I30" t="n">
-        <v>404.299538735059</v>
+        <v>405.536463435147</v>
       </c>
       <c r="J30" t="n">
-        <v>390.694712770549</v>
+        <v>405.536463435147</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121809.9976992835</v>
+        <v>125995.0451093662</v>
       </c>
       <c r="B31" t="n">
-        <v>122404.9979585527</v>
+        <v>122399.9979597393</v>
       </c>
       <c r="C31" t="n">
-        <v>122420.045954966</v>
+        <v>122415.0459561583</v>
       </c>
       <c r="D31" t="n">
-        <v>125980.0451128868</v>
+        <v>130185.04451823</v>
       </c>
       <c r="E31" t="n">
-        <v>2.14756035804748</v>
+        <v>2.20096468925476</v>
       </c>
       <c r="F31" t="n">
-        <v>2.09469246864318</v>
+        <v>2.09877777099609</v>
       </c>
       <c r="G31" t="n">
-        <v>2.10110545158386</v>
+        <v>2.14697909355163</v>
       </c>
       <c r="H31" t="n">
-        <v>2.14746499061584</v>
+        <v>2.20146083831787</v>
       </c>
       <c r="I31" t="n">
-        <v>418.485483072797</v>
+        <v>419.287383272478</v>
       </c>
       <c r="J31" t="n">
-        <v>404.648375909646</v>
+        <v>419.520448804793</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126000.0451081739</v>
+        <v>130205.0445134958</v>
       </c>
       <c r="B32" t="n">
-        <v>126594.9973674173</v>
+        <v>126609.9971638687</v>
       </c>
       <c r="C32" t="n">
-        <v>126610.0453638579</v>
+        <v>126625.0453603373</v>
       </c>
       <c r="D32" t="n">
-        <v>130190.0445170381</v>
+        <v>134375.0452252506</v>
       </c>
       <c r="E32" t="n">
-        <v>2.14746499061584</v>
+        <v>2.20159459114074</v>
       </c>
       <c r="F32" t="n">
-        <v>2.09389090538024</v>
+        <v>2.10087752342224</v>
       </c>
       <c r="G32" t="n">
-        <v>2.09631443023681</v>
+        <v>2.15398502349853</v>
       </c>
       <c r="H32" t="n">
-        <v>2.14738869667053</v>
+        <v>2.2019190788269</v>
       </c>
       <c r="I32" t="n">
-        <v>432.206274342969</v>
+        <v>433.503952466773</v>
       </c>
       <c r="J32" t="n">
-        <v>418.601756539239</v>
+        <v>433.503952466773</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130209.9965123328</v>
+        <v>134395.0452283799</v>
       </c>
       <c r="B33" t="n">
-        <v>130804.9967716114</v>
+        <v>130799.9967727889</v>
       </c>
       <c r="C33" t="n">
-        <v>130820.0447680236</v>
+        <v>130815.0447692159</v>
       </c>
       <c r="D33" t="n">
-        <v>134380.0452260329</v>
+        <v>138585.0462839543</v>
       </c>
       <c r="E33" t="n">
-        <v>2.14742684364318</v>
+        <v>2.20184278488159</v>
       </c>
       <c r="F33" t="n">
-        <v>2.09268856048584</v>
+        <v>2.10280561447143</v>
       </c>
       <c r="G33" t="n">
-        <v>2.09934949874877</v>
+        <v>2.14793348312377</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14727401733398</v>
+        <v>2.20226263999939</v>
       </c>
       <c r="I33" t="n">
-        <v>446.392197411467</v>
+        <v>447.254681100674</v>
       </c>
       <c r="J33" t="n">
-        <v>432.555106157829</v>
+        <v>447.487760539704</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134400.0452291622</v>
+        <v>138605.0462870836</v>
       </c>
       <c r="B34" t="n">
-        <v>134994.9977222497</v>
+        <v>135009.9975245965</v>
       </c>
       <c r="C34" t="n">
-        <v>135010.0457246038</v>
+        <v>135025.0457269507</v>
       </c>
       <c r="D34" t="n">
-        <v>138590.0462847366</v>
+        <v>142775.047339529</v>
       </c>
       <c r="E34" t="n">
-        <v>2.1473696231842</v>
+        <v>2.2022054195404</v>
       </c>
       <c r="F34" t="n">
-        <v>2.09278392791748</v>
+        <v>2.10416102409362</v>
       </c>
       <c r="G34" t="n">
-        <v>2.0951120853424</v>
+        <v>2.15436673164367</v>
       </c>
       <c r="H34" t="n">
-        <v>2.14763665199279</v>
+        <v>2.20239639282226</v>
       </c>
       <c r="I34" t="n">
-        <v>460.113227646581</v>
+        <v>461.471000032509</v>
       </c>
       <c r="J34" t="n">
-        <v>446.508471561733</v>
+        <v>461.471000032509</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>138609.9982878588</v>
+        <v>142795.0473426583</v>
       </c>
       <c r="B35" t="n">
-        <v>139204.9987809534</v>
+        <v>139199.9987801711</v>
       </c>
       <c r="C35" t="n">
-        <v>139220.0467833078</v>
+        <v>139215.0467825255</v>
       </c>
       <c r="D35" t="n">
-        <v>142780.0473403114</v>
+        <v>146985.0483982331</v>
       </c>
       <c r="E35" t="n">
-        <v>2.14746499061584</v>
+        <v>2.20237731933593</v>
       </c>
       <c r="F35" t="n">
-        <v>2.09077978134155</v>
+        <v>2.10549712181091</v>
       </c>
       <c r="G35" t="n">
-        <v>2.09774613380432</v>
+        <v>2.14799070358276</v>
       </c>
       <c r="H35" t="n">
-        <v>2.14691138267517</v>
+        <v>2.20243453979492</v>
       </c>
       <c r="I35" t="n">
-        <v>474.299167446783</v>
+        <v>475.222219023156</v>
       </c>
       <c r="J35" t="n">
-        <v>460.462063585472</v>
+        <v>475.455308257481</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>142800.0473434406</v>
+        <v>147005.0484013624</v>
       </c>
       <c r="B36" t="n">
-        <v>143394.9998365278</v>
+        <v>143409.999638875</v>
       </c>
       <c r="C36" t="n">
-        <v>143410.0478388826</v>
+        <v>143425.0478412295</v>
       </c>
       <c r="D36" t="n">
-        <v>146990.0483990154</v>
+        <v>151175.0494538082</v>
       </c>
       <c r="E36" t="n">
-        <v>2.14696860313415</v>
+        <v>2.20268273353576</v>
       </c>
       <c r="F36" t="n">
-        <v>2.08898591995239</v>
+        <v>2.10618448257446</v>
       </c>
       <c r="G36" t="n">
-        <v>2.09102368354797</v>
+        <v>2.1545386314392</v>
       </c>
       <c r="H36" t="n">
-        <v>2.14633893966674</v>
+        <v>2.2027781009674</v>
       </c>
       <c r="I36" t="n">
-        <v>488.019986682192</v>
+        <v>489.438825815849</v>
       </c>
       <c r="J36" t="n">
-        <v>474.415441253882</v>
+        <v>489.438825815849</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>147010.000402138</v>
+        <v>151195.0494569375</v>
       </c>
       <c r="B37" t="n">
-        <v>147605.0008952329</v>
+        <v>147600.0008944506</v>
       </c>
       <c r="C37" t="n">
-        <v>147620.0488975869</v>
+        <v>147615.0488968047</v>
       </c>
       <c r="D37" t="n">
-        <v>151180.0494545905</v>
+        <v>155385.0505125115</v>
       </c>
       <c r="E37" t="n">
-        <v>2.14620518684387</v>
+        <v>2.20275902748107</v>
       </c>
       <c r="F37" t="n">
-        <v>2.08701992034912</v>
+        <v>2.1071388721466</v>
       </c>
       <c r="G37" t="n">
-        <v>2.09436798095703</v>
+        <v>2.14762806892395</v>
       </c>
       <c r="H37" t="n">
-        <v>2.14588093757629</v>
+        <v>2.20270180702209</v>
       </c>
       <c r="I37" t="n">
-        <v>502.205887867706</v>
+        <v>503.189361890198</v>
       </c>
       <c r="J37" t="n">
-        <v>488.368816136473</v>
+        <v>503.422432094214</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>151200.0494577198</v>
+        <v>155405.0505156404</v>
       </c>
       <c r="B38" t="n">
-        <v>151795.0019508077</v>
+        <v>151810.0017531545</v>
       </c>
       <c r="C38" t="n">
-        <v>151810.0499531614</v>
+        <v>151825.0499555083</v>
       </c>
       <c r="D38" t="n">
-        <v>155390.0505132938</v>
+        <v>159575.0515680866</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1458044052124</v>
+        <v>2.20262551307678</v>
       </c>
       <c r="F38" t="n">
-        <v>2.08566498756408</v>
+        <v>2.10767340660095</v>
       </c>
       <c r="G38" t="n">
-        <v>2.08757662773132</v>
+        <v>2.15411853790283</v>
       </c>
       <c r="H38" t="n">
-        <v>2.14513635635376</v>
+        <v>2.20285439491272</v>
       </c>
       <c r="I38" t="n">
-        <v>515.926705306335</v>
+        <v>517.406226572063</v>
       </c>
       <c r="J38" t="n">
-        <v>502.32216032157</v>
+        <v>517.406226572063</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>155410.0025164164</v>
+        <v>159595.0515712159</v>
       </c>
       <c r="B39" t="n">
-        <v>156005.0030095106</v>
+        <v>156000.0030087283</v>
       </c>
       <c r="C39" t="n">
-        <v>156020.0510118647</v>
+        <v>156015.0510110827</v>
       </c>
       <c r="D39" t="n">
-        <v>159580.0515688689</v>
+        <v>163785.0526267914</v>
       </c>
       <c r="E39" t="n">
-        <v>2.14523196220397</v>
+        <v>2.20262551307678</v>
       </c>
       <c r="F39" t="n">
-        <v>2.08287835121154</v>
+        <v>2.10818886756897</v>
       </c>
       <c r="G39" t="n">
-        <v>2.09093260765075</v>
+        <v>2.14734172821044</v>
       </c>
       <c r="H39" t="n">
-        <v>2.14433479309082</v>
+        <v>2.20264458656311</v>
       </c>
       <c r="I39" t="n">
-        <v>530.1125617653259</v>
+        <v>531.157079456621</v>
       </c>
       <c r="J39" t="n">
-        <v>516.2755364565249</v>
+        <v>531.390134976513</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>159600.0515719983</v>
+        <v>163805.0526299203</v>
       </c>
       <c r="B40" t="n">
-        <v>160195.004065085</v>
+        <v>160210.0038674322</v>
       </c>
       <c r="C40" t="n">
-        <v>160210.0520674398</v>
+        <v>160225.0520697868</v>
       </c>
       <c r="D40" t="n">
-        <v>163790.0526275737</v>
+        <v>167975.0536823662</v>
       </c>
       <c r="E40" t="n">
-        <v>2.14437294006347</v>
+        <v>2.20270180702209</v>
       </c>
       <c r="F40" t="n">
-        <v>2.08037805557251</v>
+        <v>2.10820794105529</v>
       </c>
       <c r="G40" t="n">
-        <v>2.08268642425537</v>
+        <v>2.15341234207153</v>
       </c>
       <c r="H40" t="n">
-        <v>2.1435523033142</v>
+        <v>2.20293092727661</v>
       </c>
       <c r="I40" t="n">
-        <v>543.833355604011</v>
+        <v>545.373358559402</v>
       </c>
       <c r="J40" t="n">
-        <v>530.22883470947</v>
+        <v>545.373358559402</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>163810.0046306945</v>
+        <v>167995.0536854954</v>
       </c>
       <c r="B41" t="n">
-        <v>164405.0051237898</v>
+        <v>164400.0051230075</v>
       </c>
       <c r="C41" t="n">
-        <v>164420.0531261446</v>
+        <v>164415.0531253622</v>
       </c>
       <c r="D41" t="n">
-        <v>167980.0536831485</v>
+        <v>172185.0547410705</v>
       </c>
       <c r="E41" t="n">
-        <v>2.14336156845092</v>
+        <v>2.20285439491272</v>
       </c>
       <c r="F41" t="n">
-        <v>2.07845044136047</v>
+        <v>2.10914325714111</v>
       </c>
       <c r="G41" t="n">
-        <v>2.0870771408081</v>
+        <v>2.14665460586547</v>
       </c>
       <c r="H41" t="n">
-        <v>2.14303708076477</v>
+        <v>2.20283532142639</v>
       </c>
       <c r="I41" t="n">
-        <v>558.019359584392</v>
+        <v>559.123767402854</v>
       </c>
       <c r="J41" t="n">
-        <v>544.182184510322</v>
+        <v>559.356831350436</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>168000.0536862778</v>
+        <v>172205.0547441998</v>
       </c>
       <c r="B42" t="n">
-        <v>168595.0061793653</v>
+        <v>168610.0059817121</v>
       </c>
       <c r="C42" t="n">
-        <v>168610.05418172</v>
+        <v>168625.054184067</v>
       </c>
       <c r="D42" t="n">
-        <v>172190.0547418529</v>
+        <v>176375.055796646</v>
       </c>
       <c r="E42" t="n">
-        <v>2.14294171333313</v>
+        <v>2.20272088050842</v>
       </c>
       <c r="F42" t="n">
-        <v>2.07684731483459</v>
+        <v>2.10897159576416</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07931971549987</v>
+        <v>2.15299224853515</v>
       </c>
       <c r="H42" t="n">
-        <v>2.14185380935668</v>
+        <v>2.2027781009674</v>
       </c>
       <c r="I42" t="n">
-        <v>571.740161760213</v>
+        <v>573.340582110685</v>
       </c>
       <c r="J42" t="n">
-        <v>558.135634305338</v>
+        <v>573.340582110685</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>172210.0067449747</v>
+        <v>176395.055799775</v>
       </c>
       <c r="B43" t="n">
-        <v>172805.0072380693</v>
+        <v>172800.007237287</v>
       </c>
       <c r="C43" t="n">
-        <v>172820.0552404241</v>
+        <v>172815.0552396417</v>
       </c>
       <c r="D43" t="n">
-        <v>176380.0557974284</v>
+        <v>180585.0568553504</v>
       </c>
       <c r="E43" t="n">
-        <v>2.14166283607482</v>
+        <v>2.2027781009674</v>
       </c>
       <c r="F43" t="n">
-        <v>2.0760645866394</v>
+        <v>2.10920071601867</v>
       </c>
       <c r="G43" t="n">
-        <v>2.08539772033691</v>
+        <v>2.14583373069763</v>
       </c>
       <c r="H43" t="n">
-        <v>2.14137649536132</v>
+        <v>2.20260620117187</v>
       </c>
       <c r="I43" t="n">
-        <v>585.926300962307</v>
+        <v>587.091355818612</v>
       </c>
       <c r="J43" t="n">
-        <v>572.088992043133</v>
+        <v>587.324417150552</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>176400.0558005573</v>
+        <v>180605.0568584797</v>
       </c>
       <c r="B44" t="n">
-        <v>176995.0082936444</v>
+        <v>177010.0080959912</v>
       </c>
       <c r="C44" t="n">
-        <v>177010.0562959992</v>
+        <v>177025.0562983462</v>
       </c>
       <c r="D44" t="n">
-        <v>180590.0568561328</v>
+        <v>184775.0579109256</v>
       </c>
       <c r="E44" t="n">
-        <v>2.14141464233398</v>
+        <v>2.20275902748107</v>
       </c>
       <c r="F44" t="n">
-        <v>2.07572102546691</v>
+        <v>2.1090669631958</v>
       </c>
       <c r="G44" t="n">
-        <v>2.07819724082946</v>
+        <v>2.15209507942199</v>
       </c>
       <c r="H44" t="n">
-        <v>2.14053678512573</v>
+        <v>2.2027781009674</v>
       </c>
       <c r="I44" t="n">
-        <v>599.64708000106</v>
+        <v>601.308240826073</v>
       </c>
       <c r="J44" t="n">
-        <v>586.042577318158</v>
+        <v>601.308240826073</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>180610.0088592539</v>
+        <v>184795.0579140548</v>
       </c>
       <c r="B45" t="n">
-        <v>181205.0093523492</v>
+        <v>181200.0093515669</v>
       </c>
       <c r="C45" t="n">
-        <v>181220.057354704</v>
+        <v>181215.0573539216</v>
       </c>
       <c r="D45" t="n">
-        <v>184780.0579117079</v>
+        <v>188985.0589696289</v>
       </c>
       <c r="E45" t="n">
-        <v>2.14047956466674</v>
+        <v>2.20275902748107</v>
       </c>
       <c r="F45" t="n">
-        <v>2.07600736618042</v>
+        <v>2.10918164253234</v>
       </c>
       <c r="G45" t="n">
-        <v>2.08562660217285</v>
+        <v>2.14497470855712</v>
       </c>
       <c r="H45" t="n">
-        <v>2.14002156257629</v>
+        <v>2.2027781009674</v>
       </c>
       <c r="I45" t="n">
-        <v>613.832940543815</v>
+        <v>615.058870049259</v>
       </c>
       <c r="J45" t="n">
-        <v>599.995910804123</v>
+        <v>615.291948046625</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>184800.0579148372</v>
+        <v>189005.0589727582</v>
       </c>
       <c r="B46" t="n">
-        <v>185395.0104079236</v>
+        <v>185410.0102102704</v>
       </c>
       <c r="C46" t="n">
-        <v>185410.0584102783</v>
+        <v>185425.0584126253</v>
       </c>
       <c r="D46" t="n">
-        <v>188990.0589704112</v>
+        <v>193175.0600252029</v>
       </c>
       <c r="E46" t="n">
-        <v>2.14000248908996</v>
+        <v>2.20285439491272</v>
       </c>
       <c r="F46" t="n">
-        <v>2.07604551315307</v>
+        <v>2.10899066925048</v>
       </c>
       <c r="G46" t="n">
-        <v>2.07875847816467</v>
+        <v>2.15140795707702</v>
       </c>
       <c r="H46" t="n">
-        <v>2.13971614837646</v>
+        <v>2.20272088050842</v>
       </c>
       <c r="I46" t="n">
-        <v>627.553665287874</v>
+        <v>629.276013955106</v>
       </c>
       <c r="J46" t="n">
-        <v>613.949214126515</v>
+        <v>629.276013955106</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>189010.010973533</v>
+        <v>193195.0600283322</v>
       </c>
       <c r="B47" t="n">
-        <v>189605.0114666276</v>
+        <v>189600.0114658453</v>
       </c>
       <c r="C47" t="n">
-        <v>189620.059468982</v>
+        <v>189615.0594681997</v>
       </c>
       <c r="D47" t="n">
-        <v>193180.0600259852</v>
+        <v>197385.0610839066</v>
       </c>
       <c r="E47" t="n">
-        <v>2.13946795463562</v>
+        <v>2.20273995399475</v>
       </c>
       <c r="F47" t="n">
-        <v>2.07633185386657</v>
+        <v>2.10899066925048</v>
       </c>
       <c r="G47" t="n">
-        <v>2.08610391616821</v>
+        <v>2.14396286010742</v>
       </c>
       <c r="H47" t="n">
-        <v>2.13963985443115</v>
+        <v>2.20258712768554</v>
       </c>
       <c r="I47" t="n">
-        <v>641.739734093787</v>
+        <v>643.027191788065</v>
       </c>
       <c r="J47" t="n">
-        <v>627.902492921127</v>
+        <v>643.26027594478</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>193200.0600291145</v>
+        <v>197405.0610870359</v>
       </c>
       <c r="B48" t="n">
-        <v>193795.012522202</v>
+        <v>193810.0123245492</v>
       </c>
       <c r="C48" t="n">
-        <v>193810.0605245557</v>
+        <v>193825.0605269027</v>
       </c>
       <c r="D48" t="n">
-        <v>197390.0610846889</v>
+        <v>201575.062139481</v>
       </c>
       <c r="E48" t="n">
-        <v>2.13973522186279</v>
+        <v>2.20272088050842</v>
       </c>
       <c r="F48" t="n">
-        <v>2.07614111900329</v>
+        <v>2.10769248008728</v>
       </c>
       <c r="G48" t="n">
-        <v>2.07851791381835</v>
+        <v>2.15010976791381</v>
       </c>
       <c r="H48" t="n">
-        <v>2.1391053199768</v>
+        <v>2.20283532142639</v>
       </c>
       <c r="I48" t="n">
-        <v>655.4605337022419</v>
+        <v>657.245165981008</v>
       </c>
       <c r="J48" t="n">
-        <v>641.856009065173</v>
+        <v>657.245165981008</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>197410.0130878111</v>
+        <v>201595.0621426103</v>
       </c>
       <c r="B49" t="n">
-        <v>198005.0135809057</v>
+        <v>198000.0135801234</v>
       </c>
       <c r="C49" t="n">
-        <v>198020.0615832598</v>
+        <v>198015.0615824774</v>
       </c>
       <c r="D49" t="n">
-        <v>201580.0621402633</v>
+        <v>205785.0631981843</v>
       </c>
       <c r="E49" t="n">
-        <v>2.13904809951782</v>
+        <v>2.20272088050842</v>
       </c>
       <c r="F49" t="n">
-        <v>2.0753583908081</v>
+        <v>2.10845613479614</v>
       </c>
       <c r="G49" t="n">
-        <v>2.08551216125488</v>
+        <v>2.14255023002624</v>
       </c>
       <c r="H49" t="n">
-        <v>2.13914346694946</v>
+        <v>2.20283532142639</v>
       </c>
       <c r="I49" t="n">
-        <v>669.646649573661</v>
+        <v>670.996145269959</v>
       </c>
       <c r="J49" t="n">
-        <v>655.809362256892</v>
+        <v>671.229224034882</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>201600.0621433926</v>
+        <v>205805.0632013132</v>
       </c>
       <c r="B50" t="n">
-        <v>202195.0146364791</v>
+        <v>202210.0144388258</v>
       </c>
       <c r="C50" t="n">
-        <v>202210.0626388334</v>
+        <v>202225.0626411804</v>
       </c>
       <c r="D50" t="n">
-        <v>205790.0631989663</v>
+        <v>209975.0642537598</v>
       </c>
       <c r="E50" t="n">
-        <v>2.13916254043579</v>
+        <v>2.20283532142639</v>
       </c>
       <c r="F50" t="n">
-        <v>2.07514858245849</v>
+        <v>2.10834169387817</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07755589485168</v>
+        <v>2.1498806476593</v>
       </c>
       <c r="H50" t="n">
-        <v>2.13874268531799</v>
+        <v>2.20270180702209</v>
       </c>
       <c r="I50" t="n">
-        <v>683.367552363265</v>
+        <v>685.212757643532</v>
       </c>
       <c r="J50" t="n">
-        <v>669.762924692246</v>
+        <v>685.212757643532</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>205810.0152020896</v>
+        <v>209995.0642568891</v>
       </c>
       <c r="B51" t="n">
-        <v>206405.0156951841</v>
+        <v>206400.0156944018</v>
       </c>
       <c r="C51" t="n">
-        <v>206420.0636975382</v>
+        <v>206415.0636967559</v>
       </c>
       <c r="D51" t="n">
-        <v>209980.0642545421</v>
+        <v>214185.0653124638</v>
       </c>
       <c r="E51" t="n">
-        <v>2.13874268531799</v>
+        <v>2.20287346839904</v>
       </c>
       <c r="F51" t="n">
-        <v>2.07314443588256</v>
+        <v>2.10857057571411</v>
       </c>
       <c r="G51" t="n">
-        <v>2.08366084098815</v>
+        <v>2.14186310768127</v>
       </c>
       <c r="H51" t="n">
-        <v>2.13845634460449</v>
+        <v>2.20279717445373</v>
       </c>
       <c r="I51" t="n">
-        <v>697.553500293051</v>
+        <v>698.964222692939</v>
       </c>
       <c r="J51" t="n">
-        <v>683.716384168607</v>
+        <v>699.197291304292</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>210000.0642576714</v>
+        <v>214205.0653155931</v>
       </c>
       <c r="B52" t="n">
-        <v>210595.0167507596</v>
+        <v>210610.0165531064</v>
       </c>
       <c r="C52" t="n">
-        <v>210610.0647531137</v>
+        <v>210625.0647554606</v>
       </c>
       <c r="D52" t="n">
-        <v>214190.0653132462</v>
+        <v>218375.0663680382</v>
       </c>
       <c r="E52" t="n">
-        <v>2.13855195045471</v>
+        <v>2.20295000076293</v>
       </c>
       <c r="F52" t="n">
-        <v>2.07213306427002</v>
+        <v>2.10818886756897</v>
       </c>
       <c r="G52" t="n">
-        <v>2.07426929473877</v>
+        <v>2.14905977249145</v>
       </c>
       <c r="H52" t="n">
-        <v>2.13824653625488</v>
+        <v>2.20279717445373</v>
       </c>
       <c r="I52" t="n">
-        <v>711.274347484342</v>
+        <v>713.181041849197</v>
       </c>
       <c r="J52" t="n">
-        <v>697.669773630949</v>
+        <v>713.181041849197</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>214210.0173163691</v>
+        <v>218395.0663711675</v>
       </c>
       <c r="B53" t="n">
-        <v>214805.0178094637</v>
+        <v>214800.0178086814</v>
       </c>
       <c r="C53" t="n">
-        <v>214820.065811817</v>
+        <v>214815.0658110347</v>
       </c>
       <c r="D53" t="n">
-        <v>218380.0663688206</v>
+        <v>222585.067426743</v>
       </c>
       <c r="E53" t="n">
-        <v>2.13826560974121</v>
+        <v>2.20279717445373</v>
       </c>
       <c r="F53" t="n">
-        <v>2.06904101371765</v>
+        <v>2.10763525962829</v>
       </c>
       <c r="G53" t="n">
-        <v>2.08033990859985</v>
+        <v>2.14045047760009</v>
       </c>
       <c r="H53" t="n">
-        <v>2.13780760765075</v>
+        <v>2.20270180702209</v>
       </c>
       <c r="I53" t="n">
-        <v>725.460245454002</v>
+        <v>726.932592197637</v>
       </c>
       <c r="J53" t="n">
-        <v>711.623178391553</v>
+        <v>727.165668871434</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>218400.0663719499</v>
+        <v>222605.0674298719</v>
       </c>
       <c r="B54" t="n">
-        <v>218995.0188650374</v>
+        <v>219010.0186673845</v>
       </c>
       <c r="C54" t="n">
-        <v>219010.0668673918</v>
+        <v>219025.0668697387</v>
       </c>
       <c r="D54" t="n">
-        <v>222590.067427525</v>
+        <v>226775.0684823181</v>
       </c>
       <c r="E54" t="n">
-        <v>2.13788390159606</v>
+        <v>2.20279717445373</v>
       </c>
       <c r="F54" t="n">
-        <v>2.06659817695617</v>
+        <v>2.10700535774231</v>
       </c>
       <c r="G54" t="n">
-        <v>2.06873774528503</v>
+        <v>2.14781904220581</v>
       </c>
       <c r="H54" t="n">
-        <v>2.1374831199646</v>
+        <v>2.20281624794006</v>
       </c>
       <c r="I54" t="n">
-        <v>739.180953080725</v>
+        <v>741.14947354582</v>
       </c>
       <c r="J54" t="n">
-        <v>725.576518742036</v>
+        <v>741.14947354582</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>222610.0194306461</v>
+        <v>226795.0684854474</v>
       </c>
       <c r="B55" t="n">
-        <v>223205.0199237414</v>
+        <v>223200.0199229591</v>
       </c>
       <c r="C55" t="n">
-        <v>223220.0679260961</v>
+        <v>223215.0679253138</v>
       </c>
       <c r="D55" t="n">
-        <v>226780.0684831004</v>
+        <v>230985.0695410226</v>
       </c>
       <c r="E55" t="n">
-        <v>2.13736844062805</v>
+        <v>2.20272088050842</v>
       </c>
       <c r="F55" t="n">
-        <v>2.06323885917663</v>
+        <v>2.10683345794677</v>
       </c>
       <c r="G55" t="n">
-        <v>2.07524394989013</v>
+        <v>2.13919043540954</v>
       </c>
       <c r="H55" t="n">
-        <v>2.13719677925109</v>
+        <v>2.2024917602539</v>
       </c>
       <c r="I55" t="n">
-        <v>753.366749611747</v>
+        <v>754.899967906622</v>
       </c>
       <c r="J55" t="n">
-        <v>739.529780496042</v>
+        <v>755.133029967979</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>226800.0684862297</v>
+        <v>231005.0695441518</v>
       </c>
       <c r="B56" t="n">
-        <v>227395.0209793169</v>
+        <v>227410.0207816637</v>
       </c>
       <c r="C56" t="n">
-        <v>227410.0689816716</v>
+        <v>227425.0689840186</v>
       </c>
       <c r="D56" t="n">
-        <v>230990.0695418048</v>
+        <v>235175.0705965973</v>
       </c>
       <c r="E56" t="n">
-        <v>2.13715863227844</v>
+        <v>2.20256805419921</v>
       </c>
       <c r="F56" t="n">
-        <v>2.06062412261962</v>
+        <v>2.1057071685791</v>
       </c>
       <c r="G56" t="n">
-        <v>2.06264543533325</v>
+        <v>2.14640641212463</v>
       </c>
       <c r="H56" t="n">
-        <v>2.13673877716064</v>
+        <v>2.2023389339447</v>
       </c>
       <c r="I56" t="n">
-        <v>767.087447738214</v>
+        <v>769.116886399281</v>
       </c>
       <c r="J56" t="n">
-        <v>753.483021627287</v>
+        <v>769.116886399281</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>231010.0215449263</v>
+        <v>235195.0705997266</v>
       </c>
       <c r="B57" t="n">
-        <v>231605.0220380209</v>
+        <v>231600.0220372386</v>
       </c>
       <c r="C57" t="n">
-        <v>231620.0700403764</v>
+        <v>231615.0700395941</v>
       </c>
       <c r="D57" t="n">
-        <v>235180.0705973796</v>
+        <v>239385.071655302</v>
       </c>
       <c r="E57" t="n">
-        <v>2.13658595085144</v>
+        <v>2.20241546630859</v>
       </c>
       <c r="F57" t="n">
-        <v>2.05713152885437</v>
+        <v>2.10488629341125</v>
       </c>
       <c r="G57" t="n">
-        <v>2.06993818283081</v>
+        <v>2.13703346252441</v>
       </c>
       <c r="H57" t="n">
-        <v>2.13637614250183</v>
+        <v>2.2023582458496</v>
       </c>
       <c r="I57" t="n">
-        <v>781.273255932172</v>
+        <v>782.867942024219</v>
       </c>
       <c r="J57" t="n">
-        <v>767.4362746346781</v>
+        <v>783.101016840354</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>235200.0706005089</v>
+        <v>239405.0716584313</v>
       </c>
       <c r="B58" t="n">
-        <v>235795.0230935964</v>
+        <v>235810.0228959432</v>
       </c>
       <c r="C58" t="n">
-        <v>235810.0710959512</v>
+        <v>235825.0710982981</v>
       </c>
       <c r="D58" t="n">
-        <v>239390.0716560844</v>
+        <v>243575.0727108775</v>
       </c>
       <c r="E58" t="n">
-        <v>2.13643336296081</v>
+        <v>2.2022054195404</v>
       </c>
       <c r="F58" t="n">
-        <v>2.05417323112487</v>
+        <v>2.10366463661193</v>
       </c>
       <c r="G58" t="n">
-        <v>2.05575108528137</v>
+        <v>2.14468836784362</v>
       </c>
       <c r="H58" t="n">
-        <v>2.13597536087036</v>
+        <v>2.20214819908142</v>
       </c>
       <c r="I58" t="n">
-        <v>794.994039086814</v>
+        <v>797.085325169715</v>
       </c>
       <c r="J58" t="n">
-        <v>781.389528416602</v>
+        <v>797.085325169715</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>239410.0236592055</v>
+        <v>243595.0727140064</v>
       </c>
       <c r="B59" t="n">
-        <v>240005.0241523005</v>
+        <v>240000.0241515181</v>
       </c>
       <c r="C59" t="n">
-        <v>240020.0721546556</v>
+        <v>240015.0721538732</v>
       </c>
       <c r="D59" t="n">
-        <v>243580.0727116598</v>
+        <v>247785.0737695819</v>
       </c>
       <c r="E59" t="n">
-        <v>2.13591790199279</v>
+        <v>2.20222449302673</v>
       </c>
       <c r="F59" t="n">
-        <v>2.04882907867431</v>
+        <v>2.10271024703979</v>
       </c>
       <c r="G59" t="n">
-        <v>2.06249451637268</v>
+        <v>2.13455176353454</v>
       </c>
       <c r="H59" t="n">
-        <v>2.13557434082031</v>
+        <v>2.20195722579956</v>
       </c>
       <c r="I59" t="n">
-        <v>809.179889838835</v>
+        <v>810.836836756344</v>
       </c>
       <c r="J59" t="n">
-        <v>795.342867625094</v>
+        <v>811.069899205317</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>243600.0727147888</v>
+        <v>247805.0737727112</v>
       </c>
       <c r="B60" t="n">
-        <v>244195.0252078759</v>
+        <v>244210.0250102227</v>
       </c>
       <c r="C60" t="n">
-        <v>244210.0732102307</v>
+        <v>244225.0732125777</v>
       </c>
       <c r="D60" t="n">
-        <v>247790.0737703643</v>
+        <v>251975.0748251563</v>
       </c>
       <c r="E60" t="n">
-        <v>2.13584160804748</v>
+        <v>2.20214819908142</v>
       </c>
       <c r="F60" t="n">
-        <v>2.04178643226623</v>
+        <v>2.10104942321777</v>
       </c>
       <c r="G60" t="n">
-        <v>2.04244375228881</v>
+        <v>2.14255023002624</v>
       </c>
       <c r="H60" t="n">
-        <v>2.13528823852539</v>
+        <v>2.2017855644226</v>
       </c>
       <c r="I60" t="n">
-        <v>822.900611475587</v>
+        <v>825.053361018535</v>
       </c>
       <c r="J60" t="n">
-        <v>809.296162569643</v>
+        <v>825.053361018535</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>247810.0257734854</v>
+        <v>251995.0748282856</v>
       </c>
       <c r="B61" t="n">
-        <v>248405.0262665803</v>
+        <v>248400.026265798</v>
       </c>
       <c r="C61" t="n">
-        <v>248420.0742689355</v>
+        <v>248415.0742681531</v>
       </c>
       <c r="D61" t="n">
-        <v>251980.0748259386</v>
+        <v>256185.07588386</v>
       </c>
       <c r="E61" t="n">
-        <v>2.13504004478454</v>
+        <v>2.20180463790893</v>
       </c>
       <c r="F61" t="n">
-        <v>2.02793002128601</v>
+        <v>2.09935045242309</v>
       </c>
       <c r="G61" t="n">
-        <v>2.04151916503906</v>
+        <v>2.13157367706298</v>
       </c>
       <c r="H61" t="n">
-        <v>2.13488745689392</v>
+        <v>2.2014992237091</v>
       </c>
       <c r="I61" t="n">
-        <v>837.086422453991</v>
+        <v>838.804230637499</v>
       </c>
       <c r="J61" t="n">
-        <v>823.249437646587</v>
+        <v>839.037285204345</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>252000.0748290679</v>
+        <v>256205.0758869889</v>
       </c>
       <c r="B62" t="n">
-        <v>252595.0273221558</v>
+        <v>252610.0271245026</v>
       </c>
       <c r="C62" t="n">
-        <v>252610.0753245091</v>
+        <v>252625.0753268561</v>
       </c>
       <c r="D62" t="n">
-        <v>256190.0758846423</v>
+        <v>260375.0769394341</v>
       </c>
       <c r="E62" t="n">
-        <v>2.13484907150268</v>
+        <v>2.20151829719543</v>
       </c>
       <c r="F62" t="n">
-        <v>2.01233696937561</v>
+        <v>2.09656333923339</v>
       </c>
       <c r="G62" t="n">
-        <v>2.01093912124633</v>
+        <v>2.13919043540954</v>
       </c>
       <c r="H62" t="n">
-        <v>2.1343719959259</v>
+        <v>2.20123195648193</v>
       </c>
       <c r="I62" t="n">
-        <v>850.807120686991</v>
+        <v>853.020942522311</v>
       </c>
       <c r="J62" t="n">
-        <v>837.20269410044</v>
+        <v>853.020942522311</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>256210.0278877645</v>
+        <v>260395.0769425633</v>
       </c>
       <c r="B63" t="n">
-        <v>256805.0283808591</v>
+        <v>256800.0283800768</v>
       </c>
       <c r="C63" t="n">
-        <v>256820.0763832128</v>
+        <v>256815.0763824305</v>
       </c>
       <c r="D63" t="n">
-        <v>260380.0769402164</v>
+        <v>264585.1733973824</v>
       </c>
       <c r="E63" t="n">
-        <v>2.13418126106262</v>
+        <v>2.20130825042724</v>
       </c>
       <c r="F63" t="n">
-        <v>1.98805963993072</v>
+        <v>2.09404349327087</v>
       </c>
       <c r="G63" t="n">
-        <v>2.00052285194397</v>
+        <v>2.12666773796081</v>
       </c>
       <c r="H63" t="n">
-        <v>2.13370394706726</v>
+        <v>2.20090723037719</v>
       </c>
       <c r="I63" t="n">
-        <v>864.992933821896</v>
+        <v>866.7722489383031</v>
       </c>
       <c r="J63" t="n">
-        <v>851.155947291866</v>
+        <v>867.005321073962</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>260400.0769433456</v>
+        <v>264605.17418248</v>
       </c>
       <c r="B64" t="n">
-        <v>260995.0294364335</v>
+        <v>261010.02923878</v>
       </c>
       <c r="C64" t="n">
-        <v>261010.0774387876</v>
+        <v>261025.0774411345</v>
       </c>
       <c r="D64" t="n">
-        <v>264590.173593657</v>
+        <v>268775.2156755539</v>
       </c>
       <c r="E64" t="n">
-        <v>2.13378047943115</v>
+        <v>2.20113635063171</v>
       </c>
       <c r="F64" t="n">
-        <v>1.96731328964233</v>
+        <v>2.09035921096801</v>
       </c>
       <c r="G64" t="n">
-        <v>1.9658864736557</v>
+        <v>2.13470435142517</v>
       </c>
       <c r="H64" t="n">
-        <v>2.13297867774963</v>
+        <v>2.20041108131408</v>
       </c>
       <c r="I64" t="n">
-        <v>878.71356802498</v>
+        <v>880.989624144884</v>
       </c>
       <c r="J64" t="n">
-        <v>865.109206654224</v>
+        <v>880.989624144884</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>264610.0277788658</v>
+        <v>268795.2164606521</v>
       </c>
       <c r="B65" t="n">
-        <v>265205.0515355355</v>
+        <v>265200.051339261</v>
       </c>
       <c r="C65" t="n">
-        <v>265220.0761243475</v>
+        <v>265215.0759280733</v>
       </c>
       <c r="D65" t="n">
-        <v>268780.2158718284</v>
+        <v>272985.2133388542</v>
       </c>
       <c r="E65" t="n">
-        <v>2.13276886940002</v>
+        <v>2.20037293434143</v>
       </c>
       <c r="F65" t="n">
-        <v>1.94150912761688</v>
+        <v>2.08573937416076</v>
       </c>
       <c r="G65" t="n">
-        <v>1.95441126823425</v>
+        <v>2.11931824684143</v>
       </c>
       <c r="H65" t="n">
-        <v>2.13198637962341</v>
+        <v>2.19976186752319</v>
       </c>
       <c r="I65" t="n">
-        <v>892.899922297185</v>
+        <v>894.742044829801</v>
       </c>
       <c r="J65" t="n">
-        <v>879.062394358114</v>
+        <v>894.9745651230299</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>268800.216656927</v>
+        <v>273005.2141239528</v>
       </c>
       <c r="B66" t="n">
-        <v>269395.0484137423</v>
+        <v>269410.0248025797</v>
       </c>
       <c r="C66" t="n">
-        <v>269410.0730025542</v>
+        <v>269425.0735913776</v>
       </c>
       <c r="D66" t="n">
-        <v>272990.2135351284</v>
+        <v>277175.2102170549</v>
       </c>
       <c r="E66" t="n">
-        <v>2.13198637962341</v>
+        <v>2.19981932640075</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9219080209732</v>
+        <v>2.07838988304138</v>
       </c>
       <c r="G66" t="n">
-        <v>1.92123460769653</v>
+        <v>2.12630486488342</v>
       </c>
       <c r="H66" t="n">
-        <v>2.13099384307861</v>
+        <v>2.19911289215087</v>
       </c>
       <c r="I66" t="n">
-        <v>906.620593552787</v>
+        <v>908.958617077439</v>
       </c>
       <c r="J66" t="n">
-        <v>893.015640547934</v>
+        <v>908.958617077439</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>273010.0223203672</v>
+        <v>277195.2110021527</v>
       </c>
       <c r="B67" t="n">
-        <v>273605.0460770463</v>
+        <v>273600.0458807721</v>
       </c>
       <c r="C67" t="n">
-        <v>273620.0706658585</v>
+        <v>273615.0704695843</v>
       </c>
       <c r="D67" t="n">
-        <v>277180.210413329</v>
+        <v>281385.2078803591</v>
       </c>
       <c r="E67" t="n">
-        <v>2.13086032867431</v>
+        <v>2.19909381866455</v>
       </c>
       <c r="F67" t="n">
-        <v>1.90058898925781</v>
+        <v>2.07006692886352</v>
       </c>
       <c r="G67" t="n">
-        <v>1.91471254825592</v>
+        <v>2.10551643371582</v>
       </c>
       <c r="H67" t="n">
-        <v>2.12990593910217</v>
+        <v>2.19792938232421</v>
       </c>
       <c r="I67" t="n">
-        <v>920.806411098333</v>
+        <v>922.710994409048</v>
       </c>
       <c r="J67" t="n">
-        <v>906.968876105003</v>
+        <v>922.943528962165</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>277200.2111984277</v>
+        <v>281405.2086654563</v>
       </c>
       <c r="B68" t="n">
-        <v>277795.042955253</v>
+        <v>277810.0193440876</v>
       </c>
       <c r="C68" t="n">
-        <v>277810.0675440588</v>
+        <v>277825.0681328832</v>
       </c>
       <c r="D68" t="n">
-        <v>281390.2080766333</v>
+        <v>285575.2047585655</v>
       </c>
       <c r="E68" t="n">
-        <v>2.12986779212951</v>
+        <v>2.1979866027832</v>
       </c>
       <c r="F68" t="n">
-        <v>1.88543486595153</v>
+        <v>2.05756306648254</v>
       </c>
       <c r="G68" t="n">
-        <v>1.88588201999664</v>
+        <v>2.11118602752685</v>
       </c>
       <c r="H68" t="n">
-        <v>2.12860798835754</v>
+        <v>2.19645953178405</v>
       </c>
       <c r="I68" t="n">
-        <v>934.527054819418</v>
+        <v>936.92812027605</v>
       </c>
       <c r="J68" t="n">
-        <v>920.922129775782</v>
+        <v>936.92812027605</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>281410.0168618782</v>
+        <v>285595.2055436631</v>
       </c>
       <c r="B69" t="n">
-        <v>282005.0406185573</v>
+        <v>282000.0404222831</v>
       </c>
       <c r="C69" t="n">
-        <v>282020.0652073587</v>
+        <v>282015.0650110842</v>
       </c>
       <c r="D69" t="n">
-        <v>285580.2049548401</v>
+        <v>289785.2024218698</v>
       </c>
       <c r="E69" t="n">
-        <v>2.12858891487121</v>
+        <v>2.19649767875671</v>
       </c>
       <c r="F69" t="n">
-        <v>1.87203657627105</v>
+        <v>2.04011511802673</v>
       </c>
       <c r="G69" t="n">
-        <v>1.88772511482238</v>
+        <v>2.07793188095092</v>
       </c>
       <c r="H69" t="n">
-        <v>2.12771105766296</v>
+        <v>2.19439768791198</v>
       </c>
       <c r="I69" t="n">
-        <v>948.713105858996</v>
+        <v>950.679196801038</v>
       </c>
       <c r="J69" t="n">
-        <v>934.875335662872</v>
+        <v>950.911726510707</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>285600.2057399376</v>
+        <v>289805.2032069673</v>
       </c>
       <c r="B70" t="n">
-        <v>286195.0374967604</v>
+        <v>286210.0138855986</v>
       </c>
       <c r="C70" t="n">
-        <v>286210.0620855605</v>
+        <v>286225.0626743846</v>
       </c>
       <c r="D70" t="n">
-        <v>289790.2026181443</v>
+        <v>293975.1993000765</v>
       </c>
       <c r="E70" t="n">
-        <v>2.12786364555358</v>
+        <v>2.1944932937622</v>
       </c>
       <c r="F70" t="n">
-        <v>1.86377239227294</v>
+        <v>2.01153802871704</v>
       </c>
       <c r="G70" t="n">
-        <v>1.86544001102447</v>
+        <v>2.0741901397705</v>
       </c>
       <c r="H70" t="n">
-        <v>2.12641310691833</v>
+        <v>2.19170618057251</v>
       </c>
       <c r="I70" t="n">
-        <v>962.433901066117</v>
+        <v>964.895628686498</v>
       </c>
       <c r="J70" t="n">
-        <v>948.828827845894</v>
+        <v>964.895628686498</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>289810.0114033892</v>
+        <v>293995.2000851741</v>
       </c>
       <c r="B71" t="n">
-        <v>290405.035160059</v>
+        <v>290400.0349637844</v>
       </c>
       <c r="C71" t="n">
-        <v>290420.0597488611</v>
+        <v>290415.0595525866</v>
       </c>
       <c r="D71" t="n">
-        <v>293980.1994963511</v>
+        <v>298185.1969633827</v>
       </c>
       <c r="E71" t="n">
-        <v>2.12626051902771</v>
+        <v>2.19174432754516</v>
       </c>
       <c r="F71" t="n">
-        <v>1.85367596149444</v>
+        <v>1.97122061252594</v>
       </c>
       <c r="G71" t="n">
-        <v>1.87106323242187</v>
+        <v>2.01033520698547</v>
       </c>
       <c r="H71" t="n">
-        <v>2.12488627433776</v>
+        <v>2.18771648406982</v>
       </c>
       <c r="I71" t="n">
-        <v>976.619735644957</v>
+        <v>978.646704902532</v>
       </c>
       <c r="J71" t="n">
-        <v>962.782186282486</v>
+        <v>978.879222516466</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>294000.2002814487</v>
+        <v>298205.1977484801</v>
       </c>
       <c r="B72" t="n">
-        <v>294595.0320382636</v>
+        <v>294610.0084271111</v>
       </c>
       <c r="C72" t="n">
-        <v>294610.056627064</v>
+        <v>294625.0572158884</v>
       </c>
       <c r="D72" t="n">
-        <v>298190.1971596572</v>
+        <v>302375.1938415876</v>
       </c>
       <c r="E72" t="n">
-        <v>2.12479090690612</v>
+        <v>2.1877737045288</v>
       </c>
       <c r="F72" t="n">
-        <v>1.84779751300811</v>
+        <v>1.90841555595397</v>
       </c>
       <c r="G72" t="n">
-        <v>1.85020864009857</v>
+        <v>1.97790193557739</v>
       </c>
       <c r="H72" t="n">
-        <v>2.12362670898437</v>
+        <v>2.18279123306274</v>
       </c>
       <c r="I72" t="n">
-        <v>990.340559478063</v>
+        <v>992.862701368301</v>
       </c>
       <c r="J72" t="n">
-        <v>976.735454826088</v>
+        <v>992.862701368301</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>298210.0059448992</v>
+        <v>302395.1946266869</v>
       </c>
       <c r="B73" t="n">
-        <v>298805.0297015657</v>
+        <v>298800.0295052908</v>
       </c>
       <c r="C73" t="n">
-        <v>298820.0542903654</v>
+        <v>298815.0540940908</v>
       </c>
       <c r="D73" t="n">
-        <v>302380.1940378625</v>
+        <v>306585.1915048886</v>
       </c>
       <c r="E73" t="n">
-        <v>2.12362670898437</v>
+        <v>2.18286752700805</v>
       </c>
       <c r="F73" t="n">
-        <v>1.84130835533142</v>
+        <v>1.85212016105651</v>
       </c>
       <c r="G73" t="n">
-        <v>1.85987889766693</v>
+        <v>1.89133036136627</v>
       </c>
       <c r="H73" t="n">
-        <v>2.12229061126709</v>
+        <v>2.17704534530639</v>
       </c>
       <c r="I73" t="n">
-        <v>1004.52639948631</v>
+        <v>1006.61372920685</v>
       </c>
       <c r="J73" t="n">
-        <v>990.688848452079</v>
+        <v>1006.84624105568</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>302400.1948229618</v>
+        <v>306605.192289988</v>
       </c>
       <c r="B74" t="n">
-        <v>302995.0265797692</v>
+        <v>303010.0029686153</v>
       </c>
       <c r="C74" t="n">
-        <v>303010.0511685739</v>
+        <v>303025.0517573969</v>
       </c>
       <c r="D74" t="n">
-        <v>306590.1917011635</v>
+        <v>310775.1883830929</v>
       </c>
       <c r="E74" t="n">
-        <v>2.12238621711731</v>
+        <v>2.1769688129425</v>
       </c>
       <c r="F74" t="n">
-        <v>1.83672773838043</v>
+        <v>1.80158984661102</v>
       </c>
       <c r="G74" t="n">
-        <v>1.83978724479675</v>
+        <v>1.8713434934616</v>
       </c>
       <c r="H74" t="n">
-        <v>2.12066841125488</v>
+        <v>2.16948580741882</v>
       </c>
       <c r="I74" t="n">
-        <v>1018.24718004334</v>
+        <v>1020.8302313892</v>
       </c>
       <c r="J74" t="n">
-        <v>1004.6421188679</v>
+        <v>1020.8302313892</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>306610.0004864045</v>
+        <v>310795.1891681915</v>
       </c>
       <c r="B75" t="n">
-        <v>307205.0242430702</v>
+        <v>307200.0240467953</v>
       </c>
       <c r="C75" t="n">
-        <v>307220.04883188</v>
+        <v>307215.0486356054</v>
       </c>
       <c r="D75" t="n">
-        <v>310780.1885793675</v>
+        <v>314985.1860463946</v>
       </c>
       <c r="E75" t="n">
-        <v>2.12049651145935</v>
+        <v>2.1696765422821</v>
       </c>
       <c r="F75" t="n">
-        <v>1.82957053184509</v>
+        <v>1.75987899303436</v>
       </c>
       <c r="G75" t="n">
-        <v>1.84989690780639</v>
+        <v>1.7988600730896</v>
       </c>
       <c r="H75" t="n">
-        <v>2.11881709098815</v>
+        <v>2.15965461730957</v>
       </c>
       <c r="I75" t="n">
-        <v>1032.43302225408</v>
+        <v>1034.58117094851</v>
       </c>
       <c r="J75" t="n">
-        <v>1018.59546406265</v>
+        <v>1034.81367556322</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>310800.1893644664</v>
+        <v>315005.1868314933</v>
       </c>
       <c r="B76" t="n">
-        <v>311395.0211212763</v>
+        <v>311409.9975101217</v>
       </c>
       <c r="C76" t="n">
-        <v>311410.0457100886</v>
+        <v>311425.0462989115</v>
       </c>
       <c r="D76" t="n">
-        <v>314990.1862426692</v>
+        <v>319175.1829245971</v>
       </c>
       <c r="E76" t="n">
-        <v>2.11902689933776</v>
+        <v>2.15988373756408</v>
       </c>
       <c r="F76" t="n">
-        <v>1.8240737915039</v>
+        <v>1.7198097705841</v>
       </c>
       <c r="G76" t="n">
-        <v>1.82696092128753</v>
+        <v>1.78736805915832</v>
       </c>
       <c r="H76" t="n">
-        <v>2.1170802116394</v>
+        <v>2.14669275283813</v>
       </c>
       <c r="I76" t="n">
-        <v>1046.15371557926</v>
+        <v>1048.79742304904</v>
       </c>
       <c r="J76" t="n">
-        <v>1032.54874142989</v>
+        <v>1048.79742304904</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>315009.9950279083</v>
+        <v>319195.1837096961</v>
       </c>
       <c r="B77" t="n">
-        <v>315605.0187845806</v>
+        <v>315600.0185883063</v>
       </c>
       <c r="C77" t="n">
-        <v>315620.0433733928</v>
+        <v>315615.0431771183</v>
       </c>
       <c r="D77" t="n">
-        <v>319180.1831208717</v>
+        <v>323385.1805878956</v>
       </c>
       <c r="E77" t="n">
-        <v>2.11700391769409</v>
+        <v>2.14665460586547</v>
       </c>
       <c r="F77" t="n">
-        <v>1.81825256347656</v>
+        <v>1.68397855758667</v>
       </c>
       <c r="G77" t="n">
-        <v>1.84025859832763</v>
+        <v>1.72242510318756</v>
       </c>
       <c r="H77" t="n">
-        <v>2.11576318740844</v>
+        <v>2.12977933883667</v>
       </c>
       <c r="I77" t="n">
-        <v>1060.33957558114</v>
+        <v>1062.54923086931</v>
       </c>
       <c r="J77" t="n">
-        <v>1046.50199590436</v>
+        <v>1062.78174163679</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>319200.1839059706</v>
+        <v>323405.1813729949</v>
       </c>
       <c r="B78" t="n">
-        <v>319795.0156627873</v>
+        <v>319809.9920516218</v>
       </c>
       <c r="C78" t="n">
-        <v>319810.0402515996</v>
+        <v>319825.0408404226</v>
       </c>
       <c r="D78" t="n">
-        <v>323390.1807841705</v>
+        <v>327575.1774660998</v>
       </c>
       <c r="E78" t="n">
-        <v>2.11583971977233</v>
+        <v>2.13014197349548</v>
       </c>
       <c r="F78" t="n">
-        <v>1.81441628932952</v>
+        <v>1.6461237668991</v>
       </c>
       <c r="G78" t="n">
-        <v>1.81766176223754</v>
+        <v>1.71257483959198</v>
       </c>
       <c r="H78" t="n">
-        <v>2.11396932601928</v>
+        <v>2.10918164253234</v>
       </c>
       <c r="I78" t="n">
-        <v>1074.06027314203</v>
+        <v>1076.76526162825</v>
       </c>
       <c r="J78" t="n">
-        <v>1060.4552961052</v>
+        <v>1076.76526162825</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>323409.9895694125</v>
+        <v>327595.1782511974</v>
       </c>
       <c r="B79" t="n">
-        <v>324005.0133260916</v>
+        <v>324000.013129817</v>
       </c>
       <c r="C79" t="n">
-        <v>324020.037914901</v>
+        <v>324015.037718626</v>
       </c>
       <c r="D79" t="n">
-        <v>327580.1776623744</v>
+        <v>331785.1751294041</v>
       </c>
       <c r="E79" t="n">
-        <v>2.11379742622375</v>
+        <v>2.10954427719116</v>
       </c>
       <c r="F79" t="n">
-        <v>1.80737364292144</v>
+        <v>1.61006343364715</v>
       </c>
       <c r="G79" t="n">
-        <v>1.83155536651611</v>
+        <v>1.64778459072113</v>
       </c>
       <c r="H79" t="n">
-        <v>2.11141180992126</v>
+        <v>2.08554863929748</v>
       </c>
       <c r="I79" t="n">
-        <v>1088.24612934784</v>
+        <v>1090.51664164579</v>
       </c>
       <c r="J79" t="n">
-        <v>1074.40855574091</v>
+        <v>1090.74915683333</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>327600.1784474719</v>
+        <v>331805.1759145017</v>
       </c>
       <c r="B80" t="n">
-        <v>328195.0102042984</v>
+        <v>328209.9865931325</v>
       </c>
       <c r="C80" t="n">
-        <v>328210.0347931006</v>
+        <v>328225.0353819246</v>
       </c>
       <c r="D80" t="n">
-        <v>331790.1753256783</v>
+        <v>335975.1720076109</v>
       </c>
       <c r="E80" t="n">
-        <v>2.11158347129821</v>
+        <v>2.08593034744262</v>
       </c>
       <c r="F80" t="n">
-        <v>1.80080807209014</v>
+        <v>1.56875336170196</v>
       </c>
       <c r="G80" t="n">
-        <v>1.80475533008575</v>
+        <v>1.6341164112091</v>
       </c>
       <c r="H80" t="n">
-        <v>2.10862517356872</v>
+        <v>2.0580403804779</v>
       </c>
       <c r="I80" t="n">
-        <v>1101.96686357259</v>
+        <v>1104.73348840612</v>
       </c>
       <c r="J80" t="n">
-        <v>1088.36184940273</v>
+        <v>1104.73348840612</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>331809.9841109232</v>
+        <v>335995.1727927084</v>
       </c>
       <c r="B81" t="n">
-        <v>332405.0078676023</v>
+        <v>332400.0076713277</v>
       </c>
       <c r="C81" t="n">
-        <v>332420.032456402</v>
+        <v>332415.0322601274</v>
       </c>
       <c r="D81" t="n">
-        <v>335980.172203885</v>
+        <v>340185.1696709152</v>
       </c>
       <c r="E81" t="n">
-        <v>2.10849165916442</v>
+        <v>2.05851769447326</v>
       </c>
       <c r="F81" t="n">
-        <v>1.79311645030975</v>
+        <v>1.52858877182006</v>
       </c>
       <c r="G81" t="n">
-        <v>1.82023751735687</v>
+        <v>1.56539356708526</v>
       </c>
       <c r="H81" t="n">
-        <v>2.10490345954895</v>
+        <v>2.02757334709167</v>
       </c>
       <c r="I81" t="n">
-        <v>1116.15271535212</v>
+        <v>1118.48491375446</v>
       </c>
       <c r="J81" t="n">
-        <v>1102.31514768196</v>
+        <v>1118.71743165881</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>336000.1729889826</v>
+        <v>340205.1704560127</v>
       </c>
       <c r="B82" t="n">
-        <v>336595.0047458019</v>
+        <v>336609.9811346436</v>
       </c>
       <c r="C82" t="n">
-        <v>336610.0293346033</v>
+        <v>336625.0299234274</v>
       </c>
       <c r="D82" t="n">
-        <v>340190.1698671893</v>
+        <v>344375.1665491237</v>
       </c>
       <c r="E82" t="n">
-        <v>2.10511326789856</v>
+        <v>2.02820324897766</v>
       </c>
       <c r="F82" t="n">
-        <v>1.7856730222702</v>
+        <v>1.48145639896392</v>
       </c>
       <c r="G82" t="n">
-        <v>1.79008507728576</v>
+        <v>1.54510128498077</v>
       </c>
       <c r="H82" t="n">
-        <v>2.10081911087036</v>
+        <v>1.98847758769989</v>
       </c>
       <c r="I82" t="n">
-        <v>1129.87335936694</v>
+        <v>1132.70076372078</v>
       </c>
       <c r="J82" t="n">
-        <v>1116.26843466739</v>
+        <v>1132.70076372078</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>340209.9786524361</v>
+        <v>344395.1673342212</v>
       </c>
       <c r="B83" t="n">
-        <v>340805.0024091043</v>
+        <v>340800.0022128298</v>
       </c>
       <c r="C83" t="n">
-        <v>340820.0269979062</v>
+        <v>340815.0268016312</v>
       </c>
       <c r="D83" t="n">
-        <v>344380.1667453979</v>
+        <v>348585.1642124298</v>
       </c>
       <c r="E83" t="n">
-        <v>2.10058999061584</v>
+        <v>1.98926031589508</v>
       </c>
       <c r="F83" t="n">
-        <v>1.77658808231353</v>
+        <v>1.43377041816711</v>
       </c>
       <c r="G83" t="n">
-        <v>1.80752635002136</v>
+        <v>1.46973538398742</v>
       </c>
       <c r="H83" t="n">
-        <v>2.09579944610595</v>
+        <v>1.94344508647918</v>
       </c>
       <c r="I83" t="n">
-        <v>1144.05915949035</v>
+        <v>1146.45163791993</v>
       </c>
       <c r="J83" t="n">
-        <v>1130.22164119278</v>
+        <v>1146.68415067878</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>344400.1675304954</v>
+        <v>348605.1649975273</v>
       </c>
       <c r="B84" t="n">
-        <v>344994.9992873078</v>
+        <v>345009.9756761561</v>
       </c>
       <c r="C84" t="n">
-        <v>345010.0238761075</v>
+        <v>345025.0244649323</v>
       </c>
       <c r="D84" t="n">
-        <v>348590.164408704</v>
+        <v>352775.1610906315</v>
       </c>
       <c r="E84" t="n">
-        <v>2.09602856636047</v>
+        <v>1.94422781467437</v>
       </c>
       <c r="F84" t="n">
-        <v>1.76944994926452</v>
+        <v>1.37776136398315</v>
       </c>
       <c r="G84" t="n">
-        <v>1.77453315258026</v>
+        <v>1.43961191177368</v>
       </c>
       <c r="H84" t="n">
-        <v>2.09140968322753</v>
+        <v>1.88791334629058</v>
       </c>
       <c r="I84" t="n">
-        <v>1157.77997291645</v>
+        <v>1160.66808879246</v>
       </c>
       <c r="J84" t="n">
-        <v>1144.17487764483</v>
+        <v>1160.66808879246</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>348609.9731939427</v>
+        <v>352795.1618757308</v>
       </c>
       <c r="B85" t="n">
-        <v>349204.99695061</v>
+        <v>349199.9967543354</v>
       </c>
       <c r="C85" t="n">
-        <v>349220.0215394121</v>
+        <v>349215.021343138</v>
       </c>
       <c r="D85" t="n">
-        <v>352780.1612869061</v>
+        <v>356985.1587539336</v>
       </c>
       <c r="E85" t="n">
-        <v>2.09150505065918</v>
+        <v>1.88882958889007</v>
       </c>
       <c r="F85" t="n">
-        <v>1.75807476043701</v>
+        <v>1.32150423526763</v>
       </c>
       <c r="G85" t="n">
-        <v>1.79359364509582</v>
+        <v>1.35584652423858</v>
       </c>
       <c r="H85" t="n">
-        <v>2.08472967147827</v>
+        <v>1.82270300388336</v>
       </c>
       <c r="I85" t="n">
-        <v>1171.96577776382</v>
+        <v>1174.4192164988</v>
       </c>
       <c r="J85" t="n">
-        <v>1158.12825897187</v>
+        <v>1174.65172087204</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>352800.1620720054</v>
+        <v>357005.1595390323</v>
       </c>
       <c r="B86" t="n">
-        <v>353394.9938288128</v>
+        <v>353409.9702176607</v>
       </c>
       <c r="C86" t="n">
-        <v>353410.0184176207</v>
+        <v>353425.019006444</v>
       </c>
       <c r="D86" t="n">
-        <v>356990.1589502082</v>
+        <v>361105.2130842432</v>
       </c>
       <c r="E86" t="n">
-        <v>2.08511137962341</v>
+        <v>1.82369565963745</v>
       </c>
       <c r="F86" t="n">
-        <v>1.74742484092712</v>
+        <v>1.25255239009857</v>
       </c>
       <c r="G86" t="n">
-        <v>1.75344979763031</v>
+        <v>1.31045126914978</v>
       </c>
       <c r="H86" t="n">
-        <v>2.07879400253295</v>
+        <v>1.75550746917724</v>
       </c>
       <c r="I86" t="n">
-        <v>1185.68650328644</v>
+        <v>1188.635993271</v>
       </c>
       <c r="J86" t="n">
-        <v>1172.08149735522</v>
+        <v>1188.635993271</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>357009.9677354484</v>
+        <v>361125.2138693436</v>
       </c>
       <c r="B87" t="n">
-        <v>357604.9914921149</v>
+        <v>357535.0243442452</v>
       </c>
       <c r="C87" t="n">
-        <v>357620.0160809268</v>
+        <v>357545.0733367687</v>
       </c>
       <c r="D87" t="n">
-        <v>361180.1558284092</v>
+        <v>365066.0739331776</v>
       </c>
       <c r="E87" t="n">
-        <v>2.07879400253295</v>
+        <v>1.75630927085876</v>
       </c>
       <c r="F87" t="n">
-        <v>1.73595428466796</v>
+        <v>1.19999849796295</v>
       </c>
       <c r="G87" t="n">
-        <v>1.77708435058593</v>
+        <v>1.24610006809234</v>
       </c>
       <c r="H87" t="n">
-        <v>2.07253384590148</v>
+        <v>1.71326208114624</v>
       </c>
       <c r="I87" t="n">
-        <v>1199.87232021648</v>
+        <v>1200.87273690344</v>
       </c>
       <c r="J87" t="n">
-        <v>1186.0347868381</v>
+        <v>1200.87274156413</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>361200.1566135096</v>
+        <v>365086.0747182744</v>
       </c>
       <c r="B88" t="n">
-        <v>361794.988370322</v>
+        <v>361490.8851969048</v>
       </c>
       <c r="C88" t="n">
-        <v>361810.0129591332</v>
+        <v>361505.934185688</v>
       </c>
       <c r="D88" t="n">
-        <v>365390.1534917124</v>
+        <v>368966.4128271972</v>
       </c>
       <c r="E88" t="n">
-        <v>2.07287740707397</v>
+        <v>1.71425473690033</v>
       </c>
       <c r="F88" t="n">
-        <v>1.72478902339935</v>
+        <v>1.20007491111755</v>
       </c>
       <c r="G88" t="n">
-        <v>1.73188555240631</v>
+        <v>1.25260961055755</v>
       </c>
       <c r="H88" t="n">
-        <v>2.06631183624267</v>
+        <v>1.675426363945</v>
       </c>
       <c r="I88" t="n">
-        <v>1213.59307642596</v>
+        <v>1209.16631566113</v>
       </c>
       <c r="J88" t="n">
-        <v>1199.98803931487</v>
+        <v>1209.16631566113</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>365409.9622769508</v>
+        <v>368986.2216124356</v>
       </c>
       <c r="B89" t="n">
-        <v>366004.9860336252</v>
+        <v>365380.8946986096</v>
       </c>
       <c r="C89" t="n">
-        <v>366020.01062244</v>
+        <v>365386.2722946</v>
       </c>
       <c r="D89" t="n">
-        <v>369580.1503699152</v>
+        <v>372806.723565936</v>
       </c>
       <c r="E89" t="n">
-        <v>2.0664644241333</v>
+        <v>1.67620909214019</v>
       </c>
       <c r="F89" t="n">
-        <v>1.71173429489135</v>
+        <v>1.20389282703399</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7592008113861</v>
+        <v>1.21009421348571</v>
       </c>
       <c r="H89" t="n">
-        <v>2.06012797355651</v>
+        <v>1.64169490337371</v>
       </c>
       <c r="I89" t="n">
-        <v>1227.77887947937</v>
+        <v>1215.92490352341</v>
       </c>
       <c r="J89" t="n">
-        <v>1213.9413617048</v>
+        <v>1216.04910469294</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>369600.151155012</v>
+        <v>372826.7243510328</v>
       </c>
       <c r="B90" t="n">
-        <v>370194.9829118316</v>
+        <v>369241.2320224356</v>
       </c>
       <c r="C90" t="n">
-        <v>370210.0075006428</v>
+        <v>369246.5838184428</v>
       </c>
       <c r="D90" t="n">
-        <v>373790.1480332148</v>
+        <v>376647.74370414</v>
       </c>
       <c r="E90" t="n">
-        <v>2.06043338775634</v>
+        <v>1.64263033866882</v>
       </c>
       <c r="F90" t="n">
-        <v>1.70129430294036</v>
+        <v>1.20028495788574</v>
       </c>
       <c r="G90" t="n">
-        <v>1.70927906036377</v>
+        <v>1.23235547542572</v>
       </c>
       <c r="H90" t="n">
-        <v>2.05543279647827</v>
+        <v>1.61399590969085</v>
       </c>
       <c r="I90" t="n">
-        <v>1241.4996339447</v>
+        <v>1221.99202570896</v>
       </c>
       <c r="J90" t="n">
-        <v>1227.89459744396</v>
+        <v>1221.99909186633</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>373809.9568184568</v>
+        <v>376667.552489382</v>
       </c>
       <c r="B91" t="n">
-        <v>374404.9805751384</v>
+        <v>373061.5419760848</v>
       </c>
       <c r="C91" t="n">
-        <v>374420.0051639424</v>
+        <v>373067.603171568</v>
       </c>
       <c r="D91" t="n">
-        <v>377980.1449114212</v>
+        <v>380450.9942704944</v>
       </c>
       <c r="E91" t="n">
-        <v>2.05554723739624</v>
+        <v>1.61462581157684</v>
       </c>
       <c r="F91" t="n">
-        <v>1.68318176269531</v>
+        <v>1.20599269866943</v>
       </c>
       <c r="G91" t="n">
-        <v>1.7392942905426</v>
+        <v>1.21017432212829</v>
       </c>
       <c r="H91" t="n">
-        <v>2.04676795005798</v>
+        <v>1.58979022502899</v>
       </c>
       <c r="I91" t="n">
-        <v>1255.68552930718</v>
+        <v>1227.12626140066</v>
       </c>
       <c r="J91" t="n">
-        <v>1241.84792019867</v>
+        <v>1227.26639473429</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>378000.145696518</v>
+        <v>380470.8030557328</v>
       </c>
       <c r="B92" t="n">
-        <v>378594.9774533448</v>
+        <v>376862.5605440916</v>
       </c>
       <c r="C92" t="n">
-        <v>378610.0020421452</v>
+        <v>376870.8537379224</v>
       </c>
       <c r="D92" t="n">
-        <v>382190.1425747244</v>
+        <v>384231.3228539352</v>
       </c>
       <c r="E92" t="n">
-        <v>2.04718780517578</v>
+        <v>1.59038197994232</v>
       </c>
       <c r="F92" t="n">
-        <v>1.66302704811096</v>
+        <v>1.20910429954528</v>
       </c>
       <c r="G92" t="n">
-        <v>1.67336523532867</v>
+        <v>1.21049499511718</v>
       </c>
       <c r="H92" t="n">
-        <v>2.03982067108154</v>
+        <v>1.56800889968872</v>
       </c>
       <c r="I92" t="n">
-        <v>1269.40626594929</v>
+        <v>1231.81123727611</v>
       </c>
       <c r="J92" t="n">
-        <v>1255.80124803445</v>
+        <v>1232.00339660081</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>382209.95135997</v>
+        <v>384251.323639032</v>
       </c>
       <c r="B93" t="n">
-        <v>382804.9751166444</v>
+        <v>380656.1341176624</v>
       </c>
       <c r="C93" t="n">
-        <v>382819.9997054448</v>
+        <v>380671.1831064456</v>
       </c>
       <c r="D93" t="n">
-        <v>386380.1394529308</v>
+        <v>387991.6840522405</v>
       </c>
       <c r="E93" t="n">
-        <v>2.03999233245849</v>
+        <v>1.5689251422882</v>
       </c>
       <c r="F93" t="n">
-        <v>1.63903617858886</v>
+        <v>1.20003676414489</v>
       </c>
       <c r="G93" t="n">
-        <v>1.70789802074432</v>
+        <v>1.24531733989715</v>
       </c>
       <c r="H93" t="n">
-        <v>2.03212904930114</v>
+        <v>1.54914832115173</v>
       </c>
       <c r="I93" t="n">
-        <v>1283.59222936688</v>
+        <v>1236.32263959632</v>
       </c>
       <c r="J93" t="n">
-        <v>1269.75455037258</v>
+        <v>1236.32263959632</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>386400.1402380276</v>
+        <v>388011.6848373372</v>
       </c>
       <c r="B94" t="n">
-        <v>386994.9719948436</v>
+        <v>384426.1389087864</v>
       </c>
       <c r="C94" t="n">
-        <v>387009.9965836476</v>
+        <v>384431.544304758</v>
       </c>
       <c r="D94" t="n">
-        <v>390590.137116234</v>
+        <v>391754.718848556</v>
       </c>
       <c r="E94" t="n">
-        <v>2.03254890441894</v>
+        <v>1.54993104934692</v>
       </c>
       <c r="F94" t="n">
-        <v>1.60349822044372</v>
+        <v>1.20055210590362</v>
       </c>
       <c r="G94" t="n">
-        <v>1.61556649208068</v>
+        <v>1.23143923282623</v>
       </c>
       <c r="H94" t="n">
-        <v>2.02134537696838</v>
+        <v>1.53380024433136</v>
       </c>
       <c r="I94" t="n">
-        <v>1297.31299048329</v>
+        <v>1240.28443158287</v>
       </c>
       <c r="J94" t="n">
-        <v>1283.70794954077</v>
+        <v>1240.29274681325</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>390609.9459014832</v>
+        <v>391774.7196336564</v>
       </c>
       <c r="B95" t="n">
-        <v>391204.9696581468</v>
+        <v>388184.5301085576</v>
       </c>
       <c r="C95" t="n">
-        <v>391219.9942469472</v>
+        <v>388194.57910107</v>
       </c>
       <c r="D95" t="n">
-        <v>394780.133994444</v>
+        <v>395497.7970597432</v>
       </c>
       <c r="E95" t="n">
-        <v>2.02147912979126</v>
+        <v>1.53473567962646</v>
       </c>
       <c r="F95" t="n">
-        <v>1.55187094211578</v>
+        <v>1.19996035099029</v>
       </c>
       <c r="G95" t="n">
-        <v>1.63853991031646</v>
+        <v>1.23888421058654</v>
       </c>
       <c r="H95" t="n">
-        <v>2.0084433555603</v>
+        <v>1.520112991333</v>
       </c>
       <c r="I95" t="n">
-        <v>1311.49883152232</v>
+        <v>1243.97583650442</v>
       </c>
       <c r="J95" t="n">
-        <v>1297.66127192097</v>
+        <v>1243.97584116935</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>394800.1347795408</v>
+        <v>395517.7978448436</v>
       </c>
       <c r="B96" t="n">
-        <v>395394.60153663</v>
+        <v>391929.534118314</v>
       </c>
       <c r="C96" t="n">
-        <v>395404.6505291352</v>
+        <v>391937.6573122608</v>
       </c>
       <c r="D96" t="n">
-        <v>398964.7902766284</v>
+        <v>399242.4052697892</v>
       </c>
       <c r="E96" t="n">
-        <v>2.00895881652832</v>
+        <v>1.52087652683258</v>
       </c>
       <c r="F96" t="n">
-        <v>1.50003373622894</v>
+        <v>1.20412194728851</v>
       </c>
       <c r="G96" t="n">
-        <v>1.60137975215911</v>
+        <v>1.23117196559906</v>
       </c>
       <c r="H96" t="n">
-        <v>1.9941861629486</v>
+        <v>1.5083155632019</v>
       </c>
       <c r="I96" t="n">
-        <v>1325.21106094587</v>
+        <v>1247.35520476817</v>
       </c>
       <c r="J96" t="n">
-        <v>1311.61455168214</v>
+        <v>1247.42686160798</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>398984.7910617288</v>
+        <v>399262.4060548896</v>
       </c>
       <c r="B97" t="n">
-        <v>399359.6141824548</v>
+        <v>395672.2165297908</v>
       </c>
       <c r="C97" t="n">
-        <v>399366.50117733</v>
+        <v>395682.2655223068</v>
       </c>
       <c r="D97" t="n">
-        <v>402926.6409248124</v>
+        <v>402984.5442816816</v>
       </c>
       <c r="E97" t="n">
-        <v>1.99464428424835</v>
+        <v>1.5090981721878</v>
       </c>
       <c r="F97" t="n">
-        <v>1.50068259239196</v>
+        <v>1.19997942447662</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59189403057098</v>
+        <v>1.23840689659118</v>
       </c>
       <c r="H97" t="n">
-        <v>1.9911515712738</v>
+        <v>1.49775898456573</v>
       </c>
       <c r="I97" t="n">
-        <v>1333.69965078109</v>
+        <v>1250.68059907779</v>
       </c>
       <c r="J97" t="n">
-        <v>1325.21106559723</v>
+        <v>1250.68060373813</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>402946.6417099092</v>
+        <v>403004.3530669272</v>
       </c>
       <c r="B98" t="n">
-        <v>403253.6418811764</v>
+        <v>399397.2197544468</v>
       </c>
       <c r="C98" t="n">
-        <v>403268.6908699704</v>
+        <v>399404.4037490916</v>
       </c>
       <c r="D98" t="n">
-        <v>406828.8306174492</v>
+        <v>406705.1789095812</v>
       </c>
       <c r="E98" t="n">
-        <v>1.99170506000518</v>
+        <v>1.49812161922454</v>
       </c>
       <c r="F98" t="n">
-        <v>1.50011003017425</v>
+        <v>1.21051692962646</v>
       </c>
       <c r="G98" t="n">
-        <v>1.64615523815155</v>
+        <v>1.21065545082092</v>
       </c>
       <c r="H98" t="n">
-        <v>1.98899483680725</v>
+        <v>1.4897985458374</v>
       </c>
       <c r="I98" t="n">
-        <v>1340.53745992314</v>
+        <v>1253.59396182091</v>
       </c>
       <c r="J98" t="n">
-        <v>1333.74240355845</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>406848.8314025496</v>
-      </c>
-      <c r="B99" t="n">
-        <v>407063.648242494</v>
-      </c>
-      <c r="C99" t="n">
-        <v>407070.0640377216</v>
-      </c>
-      <c r="D99" t="n">
-        <v>410650.2045703044</v>
-      </c>
-      <c r="E99" t="n">
-        <v>1.98947203159332</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.50364089012146</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.52321672439575</v>
-      </c>
-      <c r="H99" t="n">
-        <v>1.98588383197784</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1345.42129202824</v>
-      </c>
-      <c r="J99" t="n">
-        <v>1340.53745992314</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>410670.0133555464</v>
-      </c>
-      <c r="B100" t="n">
-        <v>410821.4006427492</v>
-      </c>
-      <c r="C100" t="n">
-        <v>410831.4496352688</v>
-      </c>
-      <c r="D100" t="n">
-        <v>414391.5893827476</v>
-      </c>
-      <c r="E100" t="n">
-        <v>1.98594105243682</v>
-      </c>
-      <c r="F100" t="n">
-        <v>1.50003373622894</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.67884933948516</v>
-      </c>
-      <c r="H100" t="n">
-        <v>1.98517763614654</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1349.08993758143</v>
-      </c>
-      <c r="J100" t="n">
-        <v>1345.56936771912</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>414411.590167848</v>
-      </c>
-      <c r="B101" t="n">
-        <v>414521.8232857236</v>
-      </c>
-      <c r="C101" t="n">
-        <v>414531.8722782324</v>
-      </c>
-      <c r="D101" t="n">
-        <v>418092.012025722</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1.98557841777801</v>
-      </c>
-      <c r="F101" t="n">
-        <v>1.49995732307434</v>
-      </c>
-      <c r="G101" t="n">
-        <v>1.71221137046814</v>
-      </c>
-      <c r="H101" t="n">
-        <v>1.98826956748962</v>
-      </c>
-      <c r="I101" t="n">
-        <v>1351.42535549756</v>
-      </c>
-      <c r="J101" t="n">
-        <v>1349.08994223279</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>418112.0128108188</v>
-      </c>
-      <c r="B102" t="n">
-        <v>418186.824155082</v>
-      </c>
-      <c r="C102" t="n">
-        <v>418194.442149408</v>
-      </c>
-      <c r="D102" t="n">
-        <v>421754.5818968868</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1.98878490924835</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1.5040990114212</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1.70066440105438</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1.99512135982513</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1352.93701894156</v>
-      </c>
-      <c r="J102" t="n">
-        <v>1351.42536014878</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>421774.5826819836</v>
-      </c>
-      <c r="B103" t="n">
-        <v>421839.5568335748</v>
-      </c>
-      <c r="C103" t="n">
-        <v>421854.6058223688</v>
-      </c>
-      <c r="D103" t="n">
-        <v>425414.7455698476</v>
-      </c>
-      <c r="E103" t="n">
-        <v>1.99535048007965</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.50005280971527</v>
-      </c>
-      <c r="G103" t="n">
-        <v>1.80069351196289</v>
-      </c>
-      <c r="H103" t="n">
-        <v>2.00367188453674</v>
-      </c>
-      <c r="I103" t="n">
-        <v>1354.16339168461</v>
-      </c>
-      <c r="J103" t="n">
-        <v>1352.9967710976</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>425434.746354948</v>
-      </c>
-      <c r="B104" t="n">
-        <v>425480.5127208528</v>
-      </c>
-      <c r="C104" t="n">
-        <v>425495.5617096396</v>
-      </c>
-      <c r="D104" t="n">
-        <v>429055.7014571256</v>
-      </c>
-      <c r="E104" t="n">
-        <v>2.00380563735961</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.50003373622894</v>
-      </c>
-      <c r="G104" t="n">
-        <v>1.81624853610992</v>
-      </c>
-      <c r="H104" t="n">
-        <v>2.01226067543029</v>
-      </c>
-      <c r="I104" t="n">
-        <v>1355.11589547408</v>
-      </c>
-      <c r="J104" t="n">
-        <v>1354.16339168461</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>429075.7022422224</v>
-      </c>
-      <c r="B105" t="n">
-        <v>429110.512016292</v>
-      </c>
-      <c r="C105" t="n">
-        <v>429117.7076109252</v>
-      </c>
-      <c r="D105" t="n">
-        <v>432697.8481435152</v>
-      </c>
-      <c r="E105" t="n">
-        <v>2.01233696937561</v>
-      </c>
-      <c r="F105" t="n">
-        <v>1.52036011219024</v>
-      </c>
-      <c r="G105" t="n">
-        <v>1.5254613161087</v>
-      </c>
-      <c r="H105" t="n">
-        <v>2.0191695690155</v>
-      </c>
-      <c r="I105" t="n">
-        <v>1355.81359780268</v>
-      </c>
-      <c r="J105" t="n">
-        <v>1355.11589547408</v>
+        <v>1253.76026614076</v>
       </c>
     </row>
   </sheetData>
